--- a/加法实验总表.xlsx
+++ b/加法实验总表.xlsx
@@ -625,7 +625,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AW223"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="44" customWidth="1" min="2" max="2"/>

--- a/加法实验总表.xlsx
+++ b/加法实验总表.xlsx
@@ -735,7 +735,7 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>样本吞吐量 (Samples)</t>
+          <t>samples</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">

--- a/加法实验总表.xlsx
+++ b/加法实验总表.xlsx
@@ -751,7 +751,7 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>数据源参数 (data.py)</t>
+          <t>输入数据 (data.py)</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="AU3" s="7" t="inlineStr">
         <is>
-          <t>评测协议</t>
+          <t>检测数据</t>
         </is>
       </c>
       <c r="AV3" s="7" t="inlineStr">

--- a/加法实验总表.xlsx
+++ b/加法实验总表.xlsx
@@ -630,7 +630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV223"/>
+  <dimension ref="A1:AU223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -678,9 +678,8 @@
     <col width="10" customWidth="1" min="43" max="43"/>
     <col width="10" customWidth="1" min="44" max="44"/>
     <col width="10" customWidth="1" min="45" max="45"/>
-    <col width="34" customWidth="1" min="46" max="46"/>
-    <col width="10" customWidth="1" min="47" max="47"/>
-    <col width="65" customWidth="1" min="48" max="48"/>
+    <col width="10" customWidth="1" min="46" max="46"/>
+    <col width="65" customWidth="1" min="47" max="47"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -925,15 +924,10 @@
       </c>
       <c r="AT3" s="7" t="inlineStr">
         <is>
-          <t>检测数据</t>
-        </is>
-      </c>
-      <c r="AU3" s="7" t="inlineStr">
-        <is>
           <t>耗时 (s)</t>
         </is>
       </c>
-      <c r="AV3" s="8" t="inlineStr">
+      <c r="AU3" s="8" t="inlineStr">
         <is>
           <t>实测现象与表现记载 (符合预期/机制归因)</t>
         </is>
@@ -1151,15 +1145,10 @@
       </c>
       <c r="AT4" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU4" s="17" t="inlineStr">
-        <is>
           <t>138.8</t>
         </is>
       </c>
-      <c r="AV4" s="19" t="inlineStr">
+      <c r="AU4" s="19" t="inlineStr">
         <is>
           <t>层数加深不解决4位加法溢出。</t>
         </is>
@@ -1377,15 +1366,10 @@
       </c>
       <c r="AT5" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU5" s="26" t="inlineStr">
-        <is>
           <t>248.0</t>
         </is>
       </c>
-      <c r="AV5" s="27" t="inlineStr">
+      <c r="AU5" s="27" t="inlineStr">
         <is>
           <t>层数加深不解决4位加法溢出。</t>
         </is>
@@ -1603,15 +1587,10 @@
       </c>
       <c r="AT6" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU6" s="17" t="inlineStr">
-        <is>
           <t>351.1</t>
         </is>
       </c>
-      <c r="AV6" s="19" t="inlineStr">
+      <c r="AU6" s="19" t="inlineStr">
         <is>
           <t>add3相变在L2→L3(63%→93%)；sub4相变在L3→L4(67%→97%)；4位加法进位受阻与层数无单调关系。</t>
         </is>
@@ -1829,15 +1808,10 @@
       </c>
       <c r="AT7" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU7" s="26" t="inlineStr">
-        <is>
           <t>485.1</t>
         </is>
       </c>
-      <c r="AV7" s="27" t="inlineStr">
+      <c r="AU7" s="27" t="inlineStr">
         <is>
           <t>add3相变在L2→L3(63%→93%)；sub4相变在L3→L4(67%→97%)；4位加法进位受阻与层数无单调关系。</t>
         </is>
@@ -2055,15 +2029,10 @@
       </c>
       <c r="AT8" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU8" s="17" t="inlineStr">
-        <is>
           <t>562.2</t>
         </is>
       </c>
-      <c r="AV8" s="19" t="inlineStr">
+      <c r="AU8" s="19" t="inlineStr">
         <is>
           <t>层数加深不解决4位加法溢出。</t>
         </is>
@@ -2281,15 +2250,10 @@
       </c>
       <c r="AT9" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU9" s="26" t="inlineStr">
-        <is>
           <t>755.1</t>
         </is>
       </c>
-      <c r="AV9" s="27" t="inlineStr">
+      <c r="AU9" s="27" t="inlineStr">
         <is>
           <t>层数加深不解决4位加法溢出。</t>
         </is>
@@ -2507,15 +2471,10 @@
       </c>
       <c r="AT10" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU10" s="17" t="inlineStr">
-        <is>
           <t>1036.2</t>
         </is>
       </c>
-      <c r="AV10" s="19" t="inlineStr">
+      <c r="AU10" s="19" t="inlineStr">
         <is>
           <t>层数加深不解决4位加法溢出。</t>
         </is>
@@ -2733,15 +2692,10 @@
       </c>
       <c r="AT11" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU11" s="26" t="inlineStr">
-        <is>
           <t>1188.0</t>
         </is>
       </c>
-      <c r="AV11" s="27" t="inlineStr">
+      <c r="AU11" s="27" t="inlineStr">
         <is>
           <t>层数加深不解决4位加法溢出。</t>
         </is>
@@ -2959,15 +2913,10 @@
       </c>
       <c r="AT12" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU12" s="17" t="inlineStr">
-        <is>
           <t>929.7</t>
         </is>
       </c>
-      <c r="AV12" s="19" t="inlineStr">
+      <c r="AU12" s="19" t="inlineStr">
         <is>
           <t>层数加深不解决4位加法溢出。</t>
         </is>
@@ -3185,15 +3134,10 @@
       </c>
       <c r="AT13" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU13" s="26" t="inlineStr">
-        <is>
           <t>1468.7</t>
         </is>
       </c>
-      <c r="AV13" s="27" t="inlineStr">
+      <c r="AU13" s="27" t="inlineStr">
         <is>
           <t>层数加深不解决4位加法溢出。</t>
         </is>
@@ -3411,15 +3355,10 @@
       </c>
       <c r="AT14" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU14" s="17" t="inlineStr">
-        <is>
           <t>51.0</t>
         </is>
       </c>
-      <c r="AV14" s="19" t="inlineStr">
+      <c r="AU14" s="19" t="inlineStr">
         <is>
           <t>宽度增加到288后进入稳定平台。</t>
         </is>
@@ -3637,15 +3576,10 @@
       </c>
       <c r="AT15" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU15" s="26" t="inlineStr">
-        <is>
           <t>66.5</t>
         </is>
       </c>
-      <c r="AV15" s="27" t="inlineStr">
+      <c r="AU15" s="27" t="inlineStr">
         <is>
           <t>宽度增加到288后进入稳定平台。</t>
         </is>
@@ -3863,15 +3797,10 @@
       </c>
       <c r="AT16" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU16" s="17" t="inlineStr">
-        <is>
           <t>91.0</t>
         </is>
       </c>
-      <c r="AV16" s="19" t="inlineStr">
+      <c r="AU16" s="19" t="inlineStr">
         <is>
           <t>宽度增加到288后进入稳定平台。</t>
         </is>
@@ -4089,15 +4018,10 @@
       </c>
       <c r="AT17" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU17" s="26" t="inlineStr">
-        <is>
           <t>124.4</t>
         </is>
       </c>
-      <c r="AV17" s="27" t="inlineStr">
+      <c r="AU17" s="27" t="inlineStr">
         <is>
           <t>D128-D288为算术多位门槛带；D160解锁add1(97%)；D256解锁add2/3；D384 sub4达峰值87%。</t>
         </is>
@@ -4315,15 +4239,10 @@
       </c>
       <c r="AT18" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU18" s="17" t="inlineStr">
-        <is>
           <t>167.6</t>
         </is>
       </c>
-      <c r="AV18" s="19" t="inlineStr">
+      <c r="AU18" s="19" t="inlineStr">
         <is>
           <t>宽度增加到288后进入稳定平台。</t>
         </is>
@@ -4541,15 +4460,10 @@
       </c>
       <c r="AT19" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU19" s="26" t="inlineStr">
-        <is>
           <t>906.8</t>
         </is>
       </c>
-      <c r="AV19" s="27" t="inlineStr">
+      <c r="AU19" s="27" t="inlineStr">
         <is>
           <t>宽度增加到288后进入稳定平台。</t>
         </is>
@@ -4767,15 +4681,10 @@
       </c>
       <c r="AT20" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU20" s="17" t="inlineStr">
-        <is>
           <t>555.3</t>
         </is>
       </c>
-      <c r="AV20" s="19" t="inlineStr">
+      <c r="AU20" s="19" t="inlineStr">
         <is>
           <t>宽度增加到288后进入稳定平台。</t>
         </is>
@@ -4993,15 +4902,10 @@
       </c>
       <c r="AT21" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU21" s="26" t="inlineStr">
-        <is>
           <t>841.3</t>
         </is>
       </c>
-      <c r="AV21" s="27" t="inlineStr">
+      <c r="AU21" s="27" t="inlineStr">
         <is>
           <t>D128-D288为算术多位门槛带；D160解锁add1(97%)；D256解锁add2/3；D384 sub4达峰值87%。</t>
         </is>
@@ -5219,15 +5123,10 @@
       </c>
       <c r="AT22" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU22" s="17" t="inlineStr">
-        <is>
           <t>469.8</t>
         </is>
       </c>
-      <c r="AV22" s="19" t="inlineStr">
+      <c r="AU22" s="19" t="inlineStr">
         <is>
           <t>宽度增加到288后进入稳定平台。</t>
         </is>
@@ -5445,15 +5344,10 @@
       </c>
       <c r="AT23" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU23" s="26" t="inlineStr">
-        <is>
           <t>875.8</t>
         </is>
       </c>
-      <c r="AV23" s="27" t="inlineStr">
+      <c r="AU23" s="27" t="inlineStr">
         <is>
           <t>宽度增加到288后进入稳定平台。</t>
         </is>
@@ -5671,15 +5565,10 @@
       </c>
       <c r="AT24" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU24" s="17" t="inlineStr">
-        <is>
           <t>762.2</t>
         </is>
       </c>
-      <c r="AV24" s="19" t="inlineStr">
+      <c r="AU24" s="19" t="inlineStr">
         <is>
           <t>宽度增加到288后进入稳定平台。</t>
         </is>
@@ -5897,15 +5786,10 @@
       </c>
       <c r="AT25" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU25" s="26" t="inlineStr">
-        <is>
           <t>751.8</t>
         </is>
       </c>
-      <c r="AV25" s="27" t="inlineStr">
+      <c r="AU25" s="27" t="inlineStr">
         <is>
           <t>D128-D288为算术多位门槛带；D160解锁add1(97%)；D256解锁add2/3；D384 sub4达峰值87%。</t>
         </is>
@@ -6123,15 +6007,10 @@
       </c>
       <c r="AT26" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU26" s="17" t="inlineStr">
-        <is>
           <t>773.1</t>
         </is>
       </c>
-      <c r="AV26" s="19" t="inlineStr">
+      <c r="AU26" s="19" t="inlineStr">
         <is>
           <t>宽度增加到288后进入稳定平台。</t>
         </is>
@@ -6349,15 +6228,10 @@
       </c>
       <c r="AT27" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU27" s="26" t="inlineStr">
-        <is>
           <t>714.1</t>
         </is>
       </c>
-      <c r="AV27" s="27" t="inlineStr">
+      <c r="AU27" s="27" t="inlineStr">
         <is>
           <t>宽度增加到288后进入稳定平台。</t>
         </is>
@@ -6575,15 +6449,10 @@
       </c>
       <c r="AT28" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU28" s="17" t="inlineStr">
-        <is>
           <t>733.2</t>
         </is>
       </c>
-      <c r="AV28" s="19" t="inlineStr">
+      <c r="AU28" s="19" t="inlineStr">
         <is>
           <t>宽度增加到288后进入稳定平台。</t>
         </is>
@@ -6801,15 +6670,10 @@
       </c>
       <c r="AT29" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU29" s="26" t="inlineStr">
-        <is>
           <t>789.2</t>
         </is>
       </c>
-      <c r="AV29" s="27" t="inlineStr">
+      <c r="AU29" s="27" t="inlineStr">
         <is>
           <t>宽度增加到288后进入稳定平台。</t>
         </is>
@@ -7027,15 +6891,10 @@
       </c>
       <c r="AT30" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU30" s="17" t="inlineStr">
-        <is>
           <t>205.5</t>
         </is>
       </c>
-      <c r="AV30" s="19" t="inlineStr">
+      <c r="AU30" s="19" t="inlineStr">
         <is>
           <t>头数对竖式特征分割存在非单调响应。</t>
         </is>
@@ -7253,15 +7112,10 @@
       </c>
       <c r="AT31" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU31" s="26" t="inlineStr">
-        <is>
           <t>216.6</t>
         </is>
       </c>
-      <c r="AV31" s="27" t="inlineStr">
+      <c r="AU31" s="27" t="inlineStr">
         <is>
           <t>头数对竖式特征分割存在非单调响应。</t>
         </is>
@@ -7479,15 +7333,10 @@
       </c>
       <c r="AT32" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU32" s="17" t="inlineStr">
-        <is>
           <t>220.1</t>
         </is>
       </c>
-      <c r="AV32" s="19" t="inlineStr">
+      <c r="AU32" s="19" t="inlineStr">
         <is>
           <t>头数对竖式特征分割存在非单调响应。</t>
         </is>
@@ -7705,15 +7554,10 @@
       </c>
       <c r="AT33" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU33" s="26" t="inlineStr">
-        <is>
           <t>254.6</t>
         </is>
       </c>
-      <c r="AV33" s="27" t="inlineStr">
+      <c r="AU33" s="27" t="inlineStr">
         <is>
           <t>【H4甜点】add2 100%, add3 70%；H5出现奇异低谷(60%)；头数非越多越好，4头最优。</t>
         </is>
@@ -7931,15 +7775,10 @@
       </c>
       <c r="AT34" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU34" s="17" t="inlineStr">
-        <is>
           <t>362.6</t>
         </is>
       </c>
-      <c r="AV34" s="19" t="inlineStr">
+      <c r="AU34" s="19" t="inlineStr">
         <is>
           <t>头数对竖式特征分割存在非单调响应。</t>
         </is>
@@ -8157,15 +7996,10 @@
       </c>
       <c r="AT35" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU35" s="26" t="inlineStr">
-        <is>
           <t>316.9</t>
         </is>
       </c>
-      <c r="AV35" s="27" t="inlineStr">
+      <c r="AU35" s="27" t="inlineStr">
         <is>
           <t>头数对竖式特征分割存在非单调响应。</t>
         </is>
@@ -8383,15 +8217,10 @@
       </c>
       <c r="AT36" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU36" s="17" t="inlineStr">
-        <is>
           <t>437.9</t>
         </is>
       </c>
-      <c r="AV36" s="19" t="inlineStr">
+      <c r="AU36" s="19" t="inlineStr">
         <is>
           <t>头数对竖式特征分割存在非单调响应。</t>
         </is>
@@ -8609,15 +8438,10 @@
       </c>
       <c r="AT37" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU37" s="26" t="inlineStr">
-        <is>
           <t>278.7</t>
         </is>
       </c>
-      <c r="AV37" s="27" t="inlineStr">
+      <c r="AU37" s="27" t="inlineStr">
         <is>
           <t>头数对竖式特征分割存在非单调响应。</t>
         </is>
@@ -8835,15 +8659,10 @@
       </c>
       <c r="AT38" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU38" s="17" t="inlineStr">
-        <is>
           <t>433.4</t>
         </is>
       </c>
-      <c r="AV38" s="19" t="inlineStr">
+      <c r="AU38" s="19" t="inlineStr">
         <is>
           <t>dp=0.0最优；Dropout破坏进位注意力模式，开启即发生单调崩溃(add4 43%→3%→0%)。</t>
         </is>
@@ -9061,15 +8880,10 @@
       </c>
       <c r="AT39" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU39" s="26" t="inlineStr">
-        <is>
           <t>480.7</t>
         </is>
       </c>
-      <c r="AV39" s="27" t="inlineStr">
+      <c r="AU39" s="27" t="inlineStr">
         <is>
           <t>Dropout过大导致模型欠拟合并丧失算术泛化。</t>
         </is>
@@ -9287,15 +9101,10 @@
       </c>
       <c r="AT40" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU40" s="17" t="inlineStr">
-        <is>
           <t>480.4</t>
         </is>
       </c>
-      <c r="AV40" s="19" t="inlineStr">
+      <c r="AU40" s="19" t="inlineStr">
         <is>
           <t>Dropout过大导致模型欠拟合并丧失算术泛化。</t>
         </is>
@@ -9513,15 +9322,10 @@
       </c>
       <c r="AT41" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU41" s="26" t="inlineStr">
-        <is>
           <t>597.9</t>
         </is>
       </c>
-      <c r="AV41" s="27" t="inlineStr">
+      <c r="AU41" s="27" t="inlineStr">
         <is>
           <t>Dropout过大导致模型欠拟合并丧失算术泛化。</t>
         </is>
@@ -9739,15 +9543,10 @@
       </c>
       <c r="AT42" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU42" s="17" t="inlineStr">
-        <is>
           <t>616.5</t>
         </is>
       </c>
-      <c r="AV42" s="19" t="inlineStr">
+      <c r="AU42" s="19" t="inlineStr">
         <is>
           <t>Dropout过大导致模型欠拟合并丧失算术泛化。</t>
         </is>
@@ -9965,15 +9764,10 @@
       </c>
       <c r="AT43" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU43" s="26" t="inlineStr">
-        <is>
           <t>137.3</t>
         </is>
       </c>
-      <c r="AV43" s="27" t="inlineStr">
+      <c r="AU43" s="27" t="inlineStr">
         <is>
           <t>线性/滑动窗口变体在长竖式计算中存在精度折损。</t>
         </is>
@@ -10191,15 +9985,10 @@
       </c>
       <c r="AT44" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU44" s="17" t="inlineStr">
-        <is>
           <t>135.3</t>
         </is>
       </c>
-      <c r="AV44" s="19" t="inlineStr">
+      <c r="AU44" s="19" t="inlineStr">
         <is>
           <t>线性/滑动窗口变体在长竖式计算中存在精度折损。</t>
         </is>
@@ -10417,15 +10206,10 @@
       </c>
       <c r="AT45" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU45" s="26" t="inlineStr">
-        <is>
           <t>128.8</t>
         </is>
       </c>
-      <c r="AV45" s="27" t="inlineStr">
+      <c r="AU45" s="27" t="inlineStr">
         <is>
           <t>线性/滑动窗口变体在长竖式计算中存在精度折损。</t>
         </is>
@@ -10643,15 +10427,10 @@
       </c>
       <c r="AT46" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU46" s="17" t="inlineStr">
-        <is>
           <t>128.6</t>
         </is>
       </c>
-      <c r="AV46" s="19" t="inlineStr">
+      <c r="AU46" s="19" t="inlineStr">
         <is>
           <t>线性/滑动窗口变体在长竖式计算中存在精度折损。</t>
         </is>
@@ -10869,15 +10648,10 @@
       </c>
       <c r="AT47" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU47" s="26" t="inlineStr">
-        <is>
           <t>127.0</t>
         </is>
       </c>
-      <c r="AV47" s="27" t="inlineStr">
+      <c r="AU47" s="27" t="inlineStr">
         <is>
           <t>线性/滑动窗口变体在长竖式计算中存在精度折损。</t>
         </is>
@@ -11095,15 +10869,10 @@
       </c>
       <c r="AT48" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU48" s="17" t="inlineStr">
-        <is>
           <t>128.3</t>
         </is>
       </c>
-      <c r="AV48" s="19" t="inlineStr">
+      <c r="AU48" s="19" t="inlineStr">
         <is>
           <t>ALiBi相对位置偏置表现突出(add1 90%)；DSA与ALiBi显著强于标准Causal。</t>
         </is>
@@ -11321,15 +11090,10 @@
       </c>
       <c r="AT49" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU49" s="26" t="inlineStr">
-        <is>
           <t>2894.1</t>
         </is>
       </c>
-      <c r="AV49" s="27" t="inlineStr">
+      <c r="AU49" s="27" t="inlineStr">
         <is>
           <t>线性/滑动窗口变体在长竖式计算中存在精度折损。</t>
         </is>
@@ -11547,15 +11311,10 @@
       </c>
       <c r="AT50" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU50" s="17" t="inlineStr">
-        <is>
           <t>123.8</t>
         </is>
       </c>
-      <c r="AV50" s="19" t="inlineStr">
+      <c r="AU50" s="19" t="inlineStr">
         <is>
           <t>专家数增加至8-16提升了细粒度分工，E8达70%峰值，E16涌现add3。</t>
         </is>
@@ -11773,15 +11532,10 @@
       </c>
       <c r="AT51" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU51" s="26" t="inlineStr">
-        <is>
           <t>146.8</t>
         </is>
       </c>
-      <c r="AV51" s="27" t="inlineStr">
+      <c r="AU51" s="27" t="inlineStr">
         <is>
           <t>专家数增加至8-16提升了细粒度分工，E8达70%峰值，E16涌现add3。</t>
         </is>
@@ -11999,15 +11753,10 @@
       </c>
       <c r="AT52" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU52" s="17" t="inlineStr">
-        <is>
           <t>182.9</t>
         </is>
       </c>
-      <c r="AV52" s="19" t="inlineStr">
+      <c r="AU52" s="19" t="inlineStr">
         <is>
           <t>专家数增加至8-16提升了细粒度分工，E8达70%峰值，E16涌现add3。</t>
         </is>
@@ -12225,15 +11974,10 @@
       </c>
       <c r="AT53" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU53" s="26" t="inlineStr">
-        <is>
           <t>238.2</t>
         </is>
       </c>
-      <c r="AV53" s="27" t="inlineStr">
+      <c r="AU53" s="27" t="inlineStr">
         <is>
           <t>专家数增加至8-16提升了细粒度分工，E8达70%峰值，E16涌现add3。</t>
         </is>
@@ -12451,15 +12195,10 @@
       </c>
       <c r="AT54" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU54" s="17" t="inlineStr">
-        <is>
           <t>373.7</t>
         </is>
       </c>
-      <c r="AV54" s="19" t="inlineStr">
+      <c r="AU54" s="19" t="inlineStr">
         <is>
           <t>专家数增加至8-16提升了细粒度分工，E8达70%峰值，E16涌现add3。</t>
         </is>
@@ -12677,15 +12416,10 @@
       </c>
       <c r="AT55" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU55" s="26" t="inlineStr">
-        <is>
           <t>238.9</t>
         </is>
       </c>
-      <c r="AV55" s="27" t="inlineStr">
+      <c r="AU55" s="27" t="inlineStr">
         <is>
           <t>topk=4显著提升梯度路由平滑度，add1达100%。</t>
         </is>
@@ -12903,15 +12637,10 @@
       </c>
       <c r="AT56" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU56" s="17" t="inlineStr">
-        <is>
           <t>286.3</t>
         </is>
       </c>
-      <c r="AV56" s="19" t="inlineStr">
+      <c r="AU56" s="19" t="inlineStr">
         <is>
           <t>topk=4显著提升梯度路由平滑度，add1达100%。</t>
         </is>
@@ -13129,15 +12858,10 @@
       </c>
       <c r="AT57" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU57" s="26" t="inlineStr">
-        <is>
           <t>383.6</t>
         </is>
       </c>
-      <c r="AV57" s="27" t="inlineStr">
+      <c r="AU57" s="27" t="inlineStr">
         <is>
           <t>topk=4显著提升梯度路由平滑度，add1达100%。</t>
         </is>
@@ -13355,15 +13079,10 @@
       </c>
       <c r="AT58" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU58" s="17" t="inlineStr">
-        <is>
           <t>303.2</t>
         </is>
       </c>
-      <c r="AV58" s="19" t="inlineStr">
+      <c r="AU58" s="19" t="inlineStr">
         <is>
           <t>aux=1.0过强导致Loss崩溃至4.19；0.01为最佳平衡点。</t>
         </is>
@@ -13581,15 +13300,10 @@
       </c>
       <c r="AT59" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU59" s="26" t="inlineStr">
-        <is>
           <t>302.1</t>
         </is>
       </c>
-      <c r="AV59" s="27" t="inlineStr">
+      <c r="AU59" s="27" t="inlineStr">
         <is>
           <t>aux=1.0过强导致Loss崩溃至4.19；0.01为最佳平衡点。</t>
         </is>
@@ -13807,15 +13521,10 @@
       </c>
       <c r="AT60" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU60" s="17" t="inlineStr">
-        <is>
           <t>299.7</t>
         </is>
       </c>
-      <c r="AV60" s="19" t="inlineStr">
+      <c r="AU60" s="19" t="inlineStr">
         <is>
           <t>aux=1.0过强导致Loss崩溃至4.19；0.01为最佳平衡点。</t>
         </is>
@@ -14033,15 +13742,10 @@
       </c>
       <c r="AT61" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU61" s="26" t="inlineStr">
-        <is>
           <t>297.7</t>
         </is>
       </c>
-      <c r="AV61" s="27" t="inlineStr">
+      <c r="AU61" s="27" t="inlineStr">
         <is>
           <t>aux=1.0过强导致Loss崩溃至4.19；0.01为最佳平衡点。</t>
         </is>
@@ -14259,15 +13963,10 @@
       </c>
       <c r="AT62" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU62" s="17" t="inlineStr">
-        <is>
           <t>295.9</t>
         </is>
       </c>
-      <c r="AV62" s="19" t="inlineStr">
+      <c r="AU62" s="19" t="inlineStr">
         <is>
           <t>aux=1.0过强导致Loss崩溃至4.19；0.01为最佳平衡点。</t>
         </is>
@@ -14485,15 +14184,10 @@
       </c>
       <c r="AT63" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU63" s="26" t="inlineStr">
-        <is>
           <t>137.5</t>
         </is>
       </c>
-      <c r="AV63" s="27" t="inlineStr">
+      <c r="AU63" s="27" t="inlineStr">
         <is>
           <t>低秩瓶颈在残差流中提供显式维度约束。</t>
         </is>
@@ -14711,15 +14405,10 @@
       </c>
       <c r="AT64" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU64" s="17" t="inlineStr">
-        <is>
           <t>137.4</t>
         </is>
       </c>
-      <c r="AV64" s="19" t="inlineStr">
+      <c r="AU64" s="19" t="inlineStr">
         <is>
           <t>【低秩增益】b=16尾部压缩促使模型聚焦关键特征，add2提升至78%(+23pp)。</t>
         </is>
@@ -14937,15 +14626,10 @@
       </c>
       <c r="AT65" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU65" s="26" t="inlineStr">
-        <is>
           <t>147.5</t>
         </is>
       </c>
-      <c r="AV65" s="27" t="inlineStr">
+      <c r="AU65" s="27" t="inlineStr">
         <is>
           <t>低秩瓶颈在残差流中提供显式维度约束。</t>
         </is>
@@ -15163,15 +14847,10 @@
       </c>
       <c r="AT66" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU66" s="17" t="inlineStr">
-        <is>
           <t>148.8</t>
         </is>
       </c>
-      <c r="AV66" s="19" t="inlineStr">
+      <c r="AU66" s="19" t="inlineStr">
         <is>
           <t>低秩瓶颈在残差流中提供显式维度约束。</t>
         </is>
@@ -15389,15 +15068,10 @@
       </c>
       <c r="AT67" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU67" s="26" t="inlineStr">
-        <is>
           <t>122.9</t>
         </is>
       </c>
-      <c r="AV67" s="27" t="inlineStr">
+      <c r="AU67" s="27" t="inlineStr">
         <is>
           <t>瓶颈位置决定压缩是在前馈阶段还是读出阶段。</t>
         </is>
@@ -15615,15 +15289,10 @@
       </c>
       <c r="AT68" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU68" s="17" t="inlineStr">
-        <is>
           <t>134.3</t>
         </is>
       </c>
-      <c r="AV68" s="19" t="inlineStr">
+      <c r="AU68" s="19" t="inlineStr">
         <is>
           <t>【架构级证实H3】末层前插入瓶颈(last_pre)导致add2降至32%，证实末层需完整通道读答案。</t>
         </is>
@@ -15841,15 +15510,10 @@
       </c>
       <c r="AT69" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU69" s="26" t="inlineStr">
-        <is>
           <t>137.0</t>
         </is>
       </c>
-      <c r="AV69" s="27" t="inlineStr">
+      <c r="AU69" s="27" t="inlineStr">
         <is>
           <t>瓶颈位置决定压缩是在前馈阶段还是读出阶段。</t>
         </is>
@@ -16067,15 +15731,10 @@
       </c>
       <c r="AT70" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU70" s="17" t="inlineStr">
-        <is>
           <t>146.1</t>
         </is>
       </c>
-      <c r="AV70" s="19" t="inlineStr">
+      <c r="AU70" s="19" t="inlineStr">
         <is>
           <t>瓶颈位置决定压缩是在前馈阶段还是读出阶段。</t>
         </is>
@@ -16293,15 +15952,10 @@
       </c>
       <c r="AT71" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU71" s="26" t="inlineStr">
-        <is>
           <t>135.7</t>
         </is>
       </c>
-      <c r="AV71" s="27" t="inlineStr">
+      <c r="AU71" s="27" t="inlineStr">
         <is>
           <t>瓶颈位置决定压缩是在前馈阶段还是读出阶段。</t>
         </is>
@@ -16519,15 +16173,10 @@
       </c>
       <c r="AT72" s="17" t="inlineStr">
         <is>
-          <t>plain_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU72" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV72" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU72" s="19" t="inlineStr">
         <is>
           <t>【无CoT多位加法恒0%】模型只能死记1位表，无法泛化到多位进位。</t>
         </is>
@@ -16745,15 +16394,10 @@
       </c>
       <c r="AT73" s="26" t="inlineStr">
         <is>
-          <t>plain_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU73" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV73" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU73" s="27" t="inlineStr">
         <is>
           <t>【无CoT多位加法恒0%】模型只能死记1位表，无法泛化到多位进位。</t>
         </is>
@@ -16971,15 +16615,10 @@
       </c>
       <c r="AT74" s="17" t="inlineStr">
         <is>
-          <t>plain_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU74" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV74" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU74" s="19" t="inlineStr">
         <is>
           <t>【无CoT多位加法恒0%】模型只能死记1位表，无法泛化到多位进位。</t>
         </is>
@@ -17197,15 +16836,10 @@
       </c>
       <c r="AT75" s="26" t="inlineStr">
         <is>
-          <t>plain_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU75" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV75" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU75" s="27" t="inlineStr">
         <is>
           <t>【无CoT多位加法恒0%】模型只能死记1位表，无法泛化到多位进位。</t>
         </is>
@@ -17423,15 +17057,10 @@
       </c>
       <c r="AT76" s="17" t="inlineStr">
         <is>
-          <t>plain_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU76" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV76" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU76" s="19" t="inlineStr">
         <is>
           <t>【无CoT多位加法恒0%】模型只能死记1位表，无法泛化到多位进位。</t>
         </is>
@@ -17649,15 +17278,10 @@
       </c>
       <c r="AT77" s="26" t="inlineStr">
         <is>
-          <t>plain_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU77" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV77" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU77" s="27" t="inlineStr">
         <is>
           <t>【无CoT多位加法恒0%】模型只能死记1位表，无法泛化到多位进位。</t>
         </is>
@@ -17875,15 +17499,10 @@
       </c>
       <c r="AT78" s="17" t="inlineStr">
         <is>
-          <t>plain_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU78" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV78" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU78" s="19" t="inlineStr">
         <is>
           <t>【无CoT多位加法恒0%】模型只能死记1位表，无法泛化到多位进位。</t>
         </is>
@@ -18101,15 +17720,10 @@
       </c>
       <c r="AT79" s="26" t="inlineStr">
         <is>
-          <t>plain_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU79" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV79" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU79" s="27" t="inlineStr">
         <is>
           <t>【无CoT多位加法恒0%】模型只能死记1位表，无法泛化到多位进位。</t>
         </is>
@@ -18327,15 +17941,10 @@
       </c>
       <c r="AT80" s="17" t="inlineStr">
         <is>
-          <t>plain_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU80" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV80" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU80" s="19" t="inlineStr">
         <is>
           <t>【无CoT多位加法恒0%】模型只能死记1位表，无法泛化到多位进位。</t>
         </is>
@@ -18553,15 +18162,10 @@
       </c>
       <c r="AT81" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU81" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV81" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU81" s="27" t="inlineStr">
         <is>
           <t>【数据形态驱动】竖式草稿纸彻底解锁多位加减法，L1D128即达67%，L4D128全面掌握。</t>
         </is>
@@ -18779,15 +18383,10 @@
       </c>
       <c r="AT82" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU82" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV82" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU82" s="19" t="inlineStr">
         <is>
           <t>【数据形态驱动】竖式草稿纸彻底解锁多位加减法，L1D128即达67%，L4D128全面掌握。</t>
         </is>
@@ -19005,15 +18604,10 @@
       </c>
       <c r="AT83" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU83" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV83" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU83" s="27" t="inlineStr">
         <is>
           <t>【数据形态驱动】竖式草稿纸彻底解锁多位加减法，L1D128即达67%，L4D128全面掌握。</t>
         </is>
@@ -19231,15 +18825,10 @@
       </c>
       <c r="AT84" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU84" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV84" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU84" s="19" t="inlineStr">
         <is>
           <t>【数据形态驱动】竖式草稿纸彻底解锁多位加减法，L1D128即达67%，L4D128全面掌握。</t>
         </is>
@@ -19457,15 +19046,10 @@
       </c>
       <c r="AT85" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU85" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV85" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU85" s="27" t="inlineStr">
         <is>
           <t>【数据形态驱动】竖式草稿纸彻底解锁多位加减法，L1D128即达67%，L4D128全面掌握。</t>
         </is>
@@ -19683,15 +19267,10 @@
       </c>
       <c r="AT86" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU86" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV86" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU86" s="19" t="inlineStr">
         <is>
           <t>【数据形态驱动】竖式草稿纸彻底解锁多位加减法，L1D128即达67%，L4D128全面掌握。</t>
         </is>
@@ -19909,15 +19488,10 @@
       </c>
       <c r="AT87" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU87" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV87" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU87" s="27" t="inlineStr">
         <is>
           <t>【数据形态驱动】竖式草稿纸彻底解锁多位加减法，L1D128即达67%，L4D128全面掌握。</t>
         </is>
@@ -20135,15 +19709,10 @@
       </c>
       <c r="AT88" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU88" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV88" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU88" s="19" t="inlineStr">
         <is>
           <t>【数据形态驱动】竖式草稿纸彻底解锁多位加减法，L1D128即达67%，L4D128全面掌握。</t>
         </is>
@@ -20361,15 +19930,10 @@
       </c>
       <c r="AT89" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU89" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV89" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU89" s="27" t="inlineStr">
         <is>
           <t>【数据形态驱动】竖式草稿纸彻底解锁多位加减法，L1D128即达67%，L4D128全面掌握。</t>
         </is>
@@ -20587,15 +20151,10 @@
       </c>
       <c r="AT90" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU90" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV90" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU90" s="19" t="inlineStr">
         <is>
           <t>续训降低Loss并解锁sub4/add3；但add4始终≤0.47不动，4位加法进位瓶颈非步数不足所致。</t>
         </is>
@@ -20813,15 +20372,10 @@
       </c>
       <c r="AT91" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU91" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV91" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU91" s="27" t="inlineStr">
         <is>
           <t>续训降低Loss并解锁sub4/add3；但add4始终≤0.47不动，4位加法进位瓶颈非步数不足所致。</t>
         </is>
@@ -21039,15 +20593,10 @@
       </c>
       <c r="AT92" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU92" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV92" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU92" s="19" t="inlineStr">
         <is>
           <t>续训降低Loss并解锁sub4/add3；但add4始终≤0.47不动，4位加法进位瓶颈非步数不足所致。</t>
         </is>
@@ -21265,15 +20814,10 @@
       </c>
       <c r="AT93" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU93" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV93" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU93" s="27" t="inlineStr">
         <is>
           <t>续训降低Loss并解锁sub4/add3；但add4始终≤0.47不动，4位加法进位瓶颈非步数不足所致。</t>
         </is>
@@ -21491,15 +21035,10 @@
       </c>
       <c r="AT94" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU94" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV94" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU94" s="19" t="inlineStr">
         <is>
           <t>续训降低Loss并解锁sub4/add3；但add4始终≤0.47不动，4位加法进位瓶颈非步数不足所致。</t>
         </is>
@@ -21717,15 +21256,10 @@
       </c>
       <c r="AT95" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU95" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV95" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU95" s="27" t="inlineStr">
         <is>
           <t>续训降低Loss并解锁sub4/add3；但add4始终≤0.47不动，4位加法进位瓶颈非步数不足所致。</t>
         </is>
@@ -21943,15 +21477,10 @@
       </c>
       <c r="AT96" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU96" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV96" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU96" s="19" t="inlineStr">
         <is>
           <t>续训降低Loss并解锁sub4/add3；但add4始终≤0.47不动，4位加法进位瓶颈非步数不足所致。</t>
         </is>
@@ -22169,15 +21698,10 @@
       </c>
       <c r="AT97" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU97" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV97" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU97" s="27" t="inlineStr">
         <is>
           <t>续训降低Loss并解锁sub4/add3；但add4始终≤0.47不动，4位加法进位瓶颈非步数不足所致。</t>
         </is>
@@ -22395,15 +21919,10 @@
       </c>
       <c r="AT98" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU98" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV98" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU98" s="19" t="inlineStr">
         <is>
           <t>续训降低Loss并解锁sub4/add3；但add4始终≤0.47不动，4位加法进位瓶颈非步数不足所致。</t>
         </is>
@@ -22621,15 +22140,10 @@
       </c>
       <c r="AT99" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU99" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV99" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU99" s="27" t="inlineStr">
         <is>
           <t>续训降低Loss并解锁sub4/add3；但add4始终≤0.47不动，4位加法进位瓶颈非步数不足所致。</t>
         </is>
@@ -22847,15 +22361,10 @@
       </c>
       <c r="AT100" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU100" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV100" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU100" s="19" t="inlineStr">
         <is>
           <t>续训降低Loss并解锁sub4/add3；但add4始终≤0.47不动，4位加法进位瓶颈非步数不足所致。</t>
         </is>
@@ -23073,15 +22582,10 @@
       </c>
       <c r="AT101" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU101" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV101" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU101" s="27" t="inlineStr">
         <is>
           <t>续训降低Loss并解锁sub4/add3；但add4始终≤0.47不动，4位加法进位瓶颈非步数不足所致。</t>
         </is>
@@ -23299,15 +22803,10 @@
       </c>
       <c r="AT102" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU102" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV102" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU102" s="19" t="inlineStr">
         <is>
           <t>续训降低Loss并解锁sub4/add3；但add4始终≤0.47不动，4位加法进位瓶颈非步数不足所致。</t>
         </is>
@@ -23525,15 +23024,10 @@
       </c>
       <c r="AT103" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU103" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV103" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU103" s="27" t="inlineStr">
         <is>
           <t>续训降低Loss并解锁sub4/add3；但add4始终≤0.47不动，4位加法进位瓶颈非步数不足所致。</t>
         </is>
@@ -23751,15 +23245,10 @@
       </c>
       <c r="AT104" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU104" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV104" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU104" s="19" t="inlineStr">
         <is>
           <t>续训降低Loss并解锁sub4/add3；但add4始终≤0.47不动，4位加法进位瓶颈非步数不足所致。</t>
         </is>
@@ -23977,15 +23466,10 @@
       </c>
       <c r="AT105" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU105" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV105" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU105" s="27" t="inlineStr">
         <is>
           <t>续训降低Loss并解锁sub4/add3；但add4始终≤0.47不动，4位加法进位瓶颈非步数不足所致。</t>
         </is>
@@ -24203,15 +23687,10 @@
       </c>
       <c r="AT106" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU106" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV106" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU106" s="19" t="inlineStr">
         <is>
           <t>续训降低Loss并解锁sub4/add3；但add4始终≤0.47不动，4位加法进位瓶颈非步数不足所致。</t>
         </is>
@@ -24429,15 +23908,10 @@
       </c>
       <c r="AT107" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU107" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV107" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU107" s="27" t="inlineStr">
         <is>
           <t>续训降低Loss并解锁sub4/add3；但add4始终≤0.47不动，4位加法进位瓶颈非步数不足所致。</t>
         </is>
@@ -24655,15 +24129,10 @@
       </c>
       <c r="AT108" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU108" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV108" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU108" s="19" t="inlineStr">
         <is>
           <t>续训降低Loss并解锁sub4/add3；但add4始终≤0.47不动，4位加法进位瓶颈非步数不足所致。</t>
         </is>
@@ -24881,15 +24350,10 @@
       </c>
       <c r="AT109" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU109" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV109" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU109" s="27" t="inlineStr">
         <is>
           <t>续训降低Loss并解锁sub4/add3；但add4始终≤0.47不动，4位加法进位瓶颈非步数不足所致。</t>
         </is>
@@ -25107,15 +24571,10 @@
       </c>
       <c r="AT110" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU110" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV110" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU110" s="19" t="inlineStr">
         <is>
           <t>续训降低Loss并解锁sub4/add3；但add4始终≤0.47不动，4位加法进位瓶颈非步数不足所致。</t>
         </is>
@@ -25333,15 +24792,10 @@
       </c>
       <c r="AT111" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU111" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV111" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU111" s="27" t="inlineStr">
         <is>
           <t>续训降低Loss并解锁sub4/add3；但add4始终≤0.47不动，4位加法进位瓶颈非步数不足所致。</t>
         </is>
@@ -25559,15 +25013,10 @@
       </c>
       <c r="AT112" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU112" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV112" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU112" s="19" t="inlineStr">
         <is>
           <t>续训降低Loss并解锁sub4/add3；但add4始终≤0.47不动，4位加法进位瓶颈非步数不足所致。</t>
         </is>
@@ -25785,15 +25234,10 @@
       </c>
       <c r="AT113" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU113" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV113" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU113" s="27" t="inlineStr">
         <is>
           <t>续训降低Loss并解锁sub4/add3；但add4始终≤0.47不动，4位加法进位瓶颈非步数不足所致。</t>
         </is>
@@ -26011,15 +25455,10 @@
       </c>
       <c r="AT114" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU114" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV114" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU114" s="19" t="inlineStr">
         <is>
           <t>续训降低Loss并解锁sub4/add3；但add4始终≤0.47不动，4位加法进位瓶颈非步数不足所致。</t>
         </is>
@@ -26237,15 +25676,10 @@
       </c>
       <c r="AT115" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU115" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV115" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU115" s="27" t="inlineStr">
         <is>
           <t>续训降低Loss并解锁sub4/add3；但add4始终≤0.47不动，4位加法进位瓶颈非步数不足所致。</t>
         </is>
@@ -26463,15 +25897,10 @@
       </c>
       <c r="AT116" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU116" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV116" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU116" s="19" t="inlineStr">
         <is>
           <t>续训降低Loss并解锁sub4/add3；但add4始终≤0.47不动，4位加法进位瓶颈非步数不足所致。</t>
         </is>
@@ -26689,15 +26118,10 @@
       </c>
       <c r="AT117" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU117" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV117" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU117" s="27" t="inlineStr">
         <is>
           <t>续训降低Loss并解锁sub4/add3；但add4始终≤0.47不动，4位加法进位瓶颈非步数不足所致。</t>
         </is>
@@ -26915,15 +26339,10 @@
       </c>
       <c r="AT118" s="17" t="inlineStr">
         <is>
-          <t>selfplay_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU118" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV118" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU118" s="19" t="inlineStr">
         <is>
           <t>【Naive作弊】只出1位题(8+8=16)，坍缩到单点。</t>
         </is>
@@ -27141,15 +26560,10 @@
       </c>
       <c r="AT119" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU119" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV119" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU119" s="27" t="inlineStr">
         <is>
           <t>锚定杜绝1位作弊，但停在3位(882-22)依旧模式坍缩1/60。</t>
         </is>
@@ -27367,15 +26781,10 @@
       </c>
       <c r="AT120" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU120" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV120" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU120" s="19" t="inlineStr">
         <is>
           <t>记忆惩罚开始生效，唯一式由1增至4。</t>
         </is>
@@ -27593,15 +27002,10 @@
       </c>
       <c r="AT121" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU121" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV121" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU121" s="27" t="inlineStr">
         <is>
           <t>唯一式升至8/60，答案正确率保持95%。</t>
         </is>
@@ -27819,15 +27223,10 @@
       </c>
       <c r="AT122" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU122" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV122" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU122" s="19" t="inlineStr">
         <is>
           <t>【破坍缩甜点】40/60唯一算式 + 98.3%答案正确率，出题均值3.8位。</t>
         </is>
@@ -28045,15 +27444,10 @@
       </c>
       <c r="AT123" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU123" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV123" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU123" s="27" t="inlineStr">
         <is>
           <t>惩罚过重导致模型瞎出题，答案正确率崩跌至42%。</t>
         </is>
@@ -28271,15 +27665,10 @@
       </c>
       <c r="AT124" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU124" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV124" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU124" s="19" t="inlineStr">
         <is>
           <t>LRU遗忘窗口解决长训记忆库饱和，保持稳态多样性与高正确率。</t>
         </is>
@@ -28497,15 +27886,10 @@
       </c>
       <c r="AT125" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU125" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV125" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU125" s="27" t="inlineStr">
         <is>
           <t>坍缩到882-22=860，正确率100%。</t>
         </is>
@@ -28723,15 +28107,10 @@
       </c>
       <c r="AT126" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU126" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV126" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU126" s="19" t="inlineStr">
         <is>
           <t>【策略走捷径】坍缩到错式9999-11=91981，答案正确率崩为0%。</t>
         </is>
@@ -28949,15 +28328,10 @@
       </c>
       <c r="AT127" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU127" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV127" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU127" s="27" t="inlineStr">
         <is>
           <t>GRPO组内相对优势极其稳定，4位加法提升5pp且减法无回退。</t>
         </is>
@@ -29175,15 +28549,10 @@
       </c>
       <c r="AT128" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU128" s="17" t="inlineStr">
-        <is>
           <t>173.3</t>
         </is>
       </c>
-      <c r="AV128" s="19" t="inlineStr">
+      <c r="AU128" s="19" t="inlineStr">
         <is>
           <t>【符合预期/低秩欠拟合】r=1参数量仅占15.1%，低位减法出现轻度遗忘(sub1 40%)，4位加法保持46.7%不变。</t>
         </is>
@@ -29401,15 +28770,10 @@
       </c>
       <c r="AT129" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU129" s="26" t="inlineStr">
-        <is>
           <t>173.2</t>
         </is>
       </c>
-      <c r="AV129" s="27" t="inlineStr">
+      <c r="AU129" s="27" t="inlineStr">
         <is>
           <t>【符合预期/容量回升】r=2减法能力显著回暖(sub1 80%)，高位加法保持100%。</t>
         </is>
@@ -29627,15 +28991,10 @@
       </c>
       <c r="AT130" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU130" s="17" t="inlineStr">
-        <is>
           <t>174.1</t>
         </is>
       </c>
-      <c r="AV130" s="19" t="inlineStr">
+      <c r="AU130" s="19" t="inlineStr">
         <is>
           <t>【符合预期/黄金防遗忘点】r=4仅需17.4%参数即可在全4位微调下完整保底1-3位能力，兼具高算力效率。</t>
         </is>
@@ -29853,15 +29212,10 @@
       </c>
       <c r="AT131" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU131" s="26" t="inlineStr">
-        <is>
           <t>180.2</t>
         </is>
       </c>
-      <c r="AV131" s="27" t="inlineStr">
+      <c r="AU131" s="27" t="inlineStr">
         <is>
           <t>【符合预期/全量级复现】r=16性能追平全参数微调，1-3位全面恢复至100%。</t>
         </is>
@@ -30079,15 +29433,10 @@
       </c>
       <c r="AT132" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU132" s="17" t="inlineStr">
-        <is>
           <t>201.5</t>
         </is>
       </c>
-      <c r="AV132" s="19" t="inlineStr">
+      <c r="AU132" s="19" t="inlineStr">
         <is>
           <t>【超预期证实机制/容量饱和】即便是r=64消耗63%参数，add4依然严丝合缝卡在46.7%，证实微调无法超越预训练基座表征上限。</t>
         </is>
@@ -30305,15 +29654,10 @@
       </c>
       <c r="AT133" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU133" s="26" t="inlineStr">
-        <is>
           <t>895.1</t>
         </is>
       </c>
-      <c r="AV133" s="27" t="inlineStr">
+      <c r="AU133" s="27" t="inlineStr">
         <is>
           <t>【超预期发现/隐式进位上限】仅列和式(da+db=s)无显式进位，前2位依然达100%，但4位加减断崖崩跌至13-20%，证实长程级联必须显式草稿。</t>
         </is>
@@ -30531,15 +29875,10 @@
       </c>
       <c r="AT134" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU134" s="17" t="inlineStr">
-        <is>
           <t>900.5</t>
         </is>
       </c>
-      <c r="AV134" s="19" t="inlineStr">
+      <c r="AU134" s="19" t="inlineStr">
         <is>
           <t>【符合预期】包含进位项的全竖式列，add3达60%，格式复杂度略微增加注意力解析开销。</t>
         </is>
@@ -30757,15 +30096,10 @@
       </c>
       <c r="AT135" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU135" s="26" t="inlineStr">
-        <is>
           <t>910.2</t>
         </is>
       </c>
-      <c r="AV135" s="27" t="inlineStr">
+      <c r="AU135" s="27" t="inlineStr">
         <is>
           <t>【符合预期/基线表现】标准逐位进借位草稿纸，4位减法达46.7%，高位算术表征最平稳。</t>
         </is>
@@ -30983,15 +30317,10 @@
       </c>
       <c r="AT136" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU136" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV136" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU136" s="19" t="inlineStr">
         <is>
           <t>【符合预期】高位样本不足导致高位算术未解锁。</t>
         </is>
@@ -31209,15 +30538,10 @@
       </c>
       <c r="AT137" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU137" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV137" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU137" s="27" t="inlineStr">
         <is>
           <t>【符合预期】中等偏置过度区间。</t>
         </is>
@@ -31435,15 +30759,10 @@
       </c>
       <c r="AT138" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU138" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV138" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU138" s="19" t="inlineStr">
         <is>
           <t>【符合预期/黄金配比】2000步下展现出最佳的双位平衡收敛。</t>
         </is>
@@ -31661,15 +30980,10 @@
       </c>
       <c r="AT139" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU139" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV139" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU139" s="27" t="inlineStr">
         <is>
           <t>【符合预期】高位偏置过重影响基础数字对齐。</t>
         </is>
@@ -31887,15 +31201,10 @@
       </c>
       <c r="AT140" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU140" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV140" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU140" s="19" t="inlineStr">
         <is>
           <t>【超预期证实灾难性遗忘】100%全4位导致1位加减法(add1/sub1)彻底崩溃为0.0%！</t>
         </is>
@@ -32113,15 +31422,10 @@
       </c>
       <c r="AT141" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU141" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV141" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU141" s="27" t="inlineStr">
         <is>
           <t>【符合预期】极度偏向短题，1位加减法准确率高。</t>
         </is>
@@ -32339,15 +31643,10 @@
       </c>
       <c r="AT142" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU142" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV142" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU142" s="19" t="inlineStr">
         <is>
           <t>【符合预期】平滑过渡，解锁add2至10%。</t>
         </is>
@@ -32565,15 +31864,10 @@
       </c>
       <c r="AT143" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU143" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV143" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU143" s="27" t="inlineStr">
         <is>
           <t>【符合预期】标准衰减配置。</t>
         </is>
@@ -32791,15 +32085,10 @@
       </c>
       <c r="AT144" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU144" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV144" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU144" s="19" t="inlineStr">
         <is>
           <t>【符合预期】长题占比上升造成早期欠拟合。</t>
         </is>
@@ -33017,15 +32306,10 @@
       </c>
       <c r="AT145" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU145" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV145" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU145" s="27" t="inlineStr">
         <is>
           <t>【符合预期】均匀采样下长题分布空间过大，收敛显著拖慢。</t>
         </is>
@@ -33243,15 +32527,10 @@
       </c>
       <c r="AT146" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU146" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV146" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU146" s="19" t="inlineStr">
         <is>
           <t>【符合预期】从2位起衰减，短题极为集中。</t>
         </is>
@@ -33469,15 +32748,10 @@
       </c>
       <c r="AT147" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU147" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV147" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU147" s="27" t="inlineStr">
         <is>
           <t>【符合预期/标准基准】1-2位全枚举基底，3位以上平滑稀疏。</t>
         </is>
@@ -33695,15 +32969,10 @@
       </c>
       <c r="AT148" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU148" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV148" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU148" s="19" t="inlineStr">
         <is>
           <t>【符合预期】4位才衰减导致3位组合爆炸，早期收敛落后。</t>
         </is>
@@ -33921,15 +33190,10 @@
       </c>
       <c r="AT149" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU149" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV149" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU149" s="27" t="inlineStr">
         <is>
           <t>【符合预期】纯紧凑格式，缺少空格分隔导致token边界对齐较慢。</t>
         </is>
@@ -34147,15 +33411,10 @@
       </c>
       <c r="AT150" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU150" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV150" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU150" s="19" t="inlineStr">
         <is>
           <t>【符合预期】轻度空格扰动，模型具备适应力。</t>
         </is>
@@ -34373,15 +33632,10 @@
       </c>
       <c r="AT151" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU151" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV151" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU151" s="27" t="inlineStr">
         <is>
           <t>【符合预期】损失与准确率平稳。</t>
         </is>
@@ -34599,15 +33853,10 @@
       </c>
       <c r="AT152" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU152" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV152" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU152" s="19" t="inlineStr">
         <is>
           <t>【符合预期】0..3随机空格扰动下模型保持鲁棒。</t>
         </is>
@@ -34825,15 +34074,10 @@
       </c>
       <c r="AT153" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU153" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV153" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU153" s="27" t="inlineStr">
         <is>
           <t>【符合预期/单样本最优】单题单行消除跨样本因果干扰，高位加减法大幅领先打包模式。</t>
         </is>
@@ -35051,15 +34295,10 @@
       </c>
       <c r="AT154" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU154" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV154" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU154" s="19" t="inlineStr">
         <is>
           <t>【符合预期】小窗口打包，4位加法出现显著退化(30%→3.3%)。</t>
         </is>
@@ -35277,15 +34516,10 @@
       </c>
       <c r="AT155" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU155" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV155" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU155" s="27" t="inlineStr">
         <is>
           <t>【符合预期】跨序列注意力混杂加剧，多位加法降至10%。</t>
         </is>
@@ -35503,15 +34737,10 @@
       </c>
       <c r="AT156" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU156" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV156" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU156" s="19" t="inlineStr">
         <is>
           <t>【符合预期】长窗口全量拼接导致小模型信噪比严重不足。</t>
         </is>
@@ -35729,15 +34958,10 @@
       </c>
       <c r="AT157" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU157" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV157" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU157" s="27" t="inlineStr">
         <is>
           <t>【符合预期/基线标配】余弦平滑退火，梯度最稳定。</t>
         </is>
@@ -35955,15 +35179,10 @@
       </c>
       <c r="AT158" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU158" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV158" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU158" s="19" t="inlineStr">
         <is>
           <t>【符合预期】线性衰减末期步长偏大，略逊于余弦。</t>
         </is>
@@ -36181,15 +35400,10 @@
       </c>
       <c r="AT159" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU159" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV159" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU159" s="27" t="inlineStr">
         <is>
           <t>【符合预期】无预热余弦退火，初期收敛略快但抗冲击性弱。</t>
         </is>
@@ -36407,15 +35621,10 @@
       </c>
       <c r="AT160" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU160" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV160" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU160" s="19" t="inlineStr">
         <is>
           <t>【符合预期】纯线性调度，表现平稳。</t>
         </is>
@@ -36633,15 +35842,10 @@
       </c>
       <c r="AT161" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU161" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV161" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU161" s="27" t="inlineStr">
         <is>
           <t>【符合预期】常数学习率末期无法精细收敛，损失最高。</t>
         </is>
@@ -36859,15 +36063,10 @@
       </c>
       <c r="AT162" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU162" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV162" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU162" s="19" t="inlineStr">
         <is>
           <t>【符合预期】标准动量组合。</t>
         </is>
@@ -37085,15 +36284,10 @@
       </c>
       <c r="AT163" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU163" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV163" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU163" s="27" t="inlineStr">
         <is>
           <t>【符合预期】过渡档位。</t>
         </is>
@@ -37311,15 +36505,10 @@
       </c>
       <c r="AT164" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU164" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV164" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU164" s="19" t="inlineStr">
         <is>
           <t>【符合预期】稍大二阶动量，损失降至0.462。</t>
         </is>
@@ -37537,15 +36726,10 @@
       </c>
       <c r="AT165" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU165" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV165" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU165" s="27" t="inlineStr">
         <is>
           <t>【符合预期】PyTorch默认，表现平稳。</t>
         </is>
@@ -37763,15 +36947,10 @@
       </c>
       <c r="AT166" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU166" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV166" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU166" s="19" t="inlineStr">
         <is>
           <t>【符合预期】一阶动量0.95下平滑度高。</t>
         </is>
@@ -37989,15 +37168,10 @@
       </c>
       <c r="AT167" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU167" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV167" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU167" s="27" t="inlineStr">
         <is>
           <t>【符合预期】强裁剪未造成负面影响。</t>
         </is>
@@ -38215,15 +37389,10 @@
       </c>
       <c r="AT168" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU168" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV168" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU168" s="19" t="inlineStr">
         <is>
           <t>【符合预期/标准基线】裁剪阈值1.0稳定收敛。</t>
         </is>
@@ -38441,15 +37610,10 @@
       </c>
       <c r="AT169" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU169" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV169" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU169" s="27" t="inlineStr">
         <is>
           <t>【符合预期】弱敏感。</t>
         </is>
@@ -38667,15 +37831,10 @@
       </c>
       <c r="AT170" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU170" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV170" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU170" s="19" t="inlineStr">
         <is>
           <t>【符合预期】梯度极少超过1.0，高阈值表现一致。</t>
         </is>
@@ -38893,15 +38052,10 @@
       </c>
       <c r="AT171" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU171" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV171" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU171" s="27" t="inlineStr">
         <is>
           <t>【符合预期】收敛平稳但速度略慢。</t>
         </is>
@@ -39119,15 +38273,10 @@
       </c>
       <c r="AT172" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU172" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV172" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU172" s="19" t="inlineStr">
         <is>
           <t>【符合预期】接近最佳区域。</t>
         </is>
@@ -39345,15 +38494,10 @@
       </c>
       <c r="AT173" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU173" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV173" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU173" s="27" t="inlineStr">
         <is>
           <t>【符合预期/绝对甜点】兼具收敛速度与解题精度。</t>
         </is>
@@ -39571,15 +38715,10 @@
       </c>
       <c r="AT174" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU174" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV174" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU174" s="19" t="inlineStr">
         <is>
           <t>【符合预期】高位略有扰动但可用。</t>
         </is>
@@ -39797,15 +38936,10 @@
       </c>
       <c r="AT175" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU175" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV175" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU175" s="27" t="inlineStr">
         <is>
           <t>【符合预期】学习率偏大引起局部跳跃。</t>
         </is>
@@ -40023,15 +39157,10 @@
       </c>
       <c r="AT176" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU176" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV176" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU176" s="19" t="inlineStr">
         <is>
           <t>【符合预期】剧烈振荡，精度崩塌。</t>
         </is>
@@ -40249,15 +39378,10 @@
       </c>
       <c r="AT177" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU177" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV177" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU177" s="27" t="inlineStr">
         <is>
           <t>【符合预期】完全发散。</t>
         </is>
@@ -40475,15 +39599,10 @@
       </c>
       <c r="AT178" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU178" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV178" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU178" s="19" t="inlineStr">
         <is>
           <t>【符合预期】无权重衰减，缺乏范数收缩。</t>
         </is>
@@ -40701,15 +39820,10 @@
       </c>
       <c r="AT179" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU179" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV179" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU179" s="27" t="inlineStr">
         <is>
           <t>【符合预期】轻度正则化。</t>
         </is>
@@ -40927,15 +40041,10 @@
       </c>
       <c r="AT180" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU180" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV180" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU180" s="19" t="inlineStr">
         <is>
           <t>【符合预期/最佳正则点】有效约束嵌入与注意力和。</t>
         </is>
@@ -41153,15 +40262,10 @@
       </c>
       <c r="AT181" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU181" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV181" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU181" s="27" t="inlineStr">
         <is>
           <t>【符合预期】衰减过大造成欠拟合。</t>
         </is>
@@ -41379,15 +40483,10 @@
       </c>
       <c r="AT182" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU182" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV182" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU182" s="19" t="inlineStr">
         <is>
           <t>【符合预期】256长度对单题CoT完全足够。</t>
         </is>
@@ -41605,15 +40704,10 @@
       </c>
       <c r="AT183" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU183" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV183" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU183" s="27" t="inlineStr">
         <is>
           <t>【符合预期】表现一致。</t>
         </is>
@@ -41831,15 +40925,10 @@
       </c>
       <c r="AT184" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU184" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV184" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU184" s="19" t="inlineStr">
         <is>
           <t>【符合预期/统计稳健】seed 0基线。</t>
         </is>
@@ -42057,15 +41146,10 @@
       </c>
       <c r="AT185" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU185" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV185" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU185" s="27" t="inlineStr">
         <is>
           <t>【符合预期/统计稳健】seed 1损失与结构高度一致。</t>
         </is>
@@ -42283,15 +41367,10 @@
       </c>
       <c r="AT186" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU186" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV186" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU186" s="19" t="inlineStr">
         <is>
           <t>【符合预期/统计稳健】seed 42复现，波动小于3%。</t>
         </is>
@@ -42509,15 +41588,10 @@
       </c>
       <c r="AT187" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4 + eval=5..7)</t>
-        </is>
-      </c>
-      <c r="AU187" s="26" t="inlineStr">
-        <is>
           <t>487.8</t>
         </is>
       </c>
-      <c r="AV187" s="27" t="inlineStr">
+      <c r="AU187" s="27" t="inlineStr">
         <is>
           <t>【重大反直觉证伪/外推瓶颈不在位置编码】分布内表现优异(add4 46.7%)，但外推5/6/7位准确率全部为0.0%！原本假设相对位置能泛化，实测证伪：算术外推失败源于自回归草稿纸模板未泛化为状态机。</t>
         </is>
@@ -42735,15 +41809,10 @@
       </c>
       <c r="AT188" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU188" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV188" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU188" s="19" t="inlineStr">
         <is>
           <t>【符合预期】中等遗忘窗口，出题保持多样性(52/60唯一)，均值2.98位。</t>
         </is>
@@ -42961,15 +42030,10 @@
       </c>
       <c r="AT189" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU189" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV189" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU189" s="27" t="inlineStr">
         <is>
           <t>【超预期提升】超大滑动窗口阻断长期重复，多样性跃升至57/60。</t>
         </is>
@@ -43187,15 +42251,10 @@
       </c>
       <c r="AT190" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU190" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV190" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU190" s="19" t="inlineStr">
         <is>
           <t>【符合预期】动态课程引导避免单点坍缩，出题均值2.45位。</t>
         </is>
@@ -43413,15 +42472,10 @@
       </c>
       <c r="AT191" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU191" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV191" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU191" s="27" t="inlineStr">
         <is>
           <t>【符合预期】强制抛弃1位题，保持33/60多样性。</t>
         </is>
@@ -43639,15 +42693,10 @@
       </c>
       <c r="AT192" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU192" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV192" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU192" s="19" t="inlineStr">
         <is>
           <t>【超预期/黄金学习率】极其平缓的策略更新，达成59/60接近全散开多样性与高正确率。</t>
         </is>
@@ -43865,15 +42914,10 @@
       </c>
       <c r="AT193" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU193" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV193" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU193" s="27" t="inlineStr">
         <is>
           <t>【符合预期】略大步长引发局部坍缩至4位单题。</t>
         </is>
@@ -44091,15 +43135,10 @@
       </c>
       <c r="AT194" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU194" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV194" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU194" s="19" t="inlineStr">
         <is>
           <t>【符合预期/策略漂移】出题完全散开(57/60)，但解题能力被过大梯度冲垮。</t>
         </is>
@@ -44317,15 +43356,10 @@
       </c>
       <c r="AT195" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU195" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV195" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU195" s="27" t="inlineStr">
         <is>
           <t>【符合预期】记忆按0.9衰减，维持在4位题带。</t>
         </is>
@@ -44543,15 +43577,10 @@
       </c>
       <c r="AT196" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU196" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV196" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU196" s="19" t="inlineStr">
         <is>
           <t>【符合预期】持续约束生成空间。</t>
         </is>
@@ -44769,15 +43798,10 @@
       </c>
       <c r="AT197" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU197" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV197" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU197" s="27" t="inlineStr">
         <is>
           <t>【符合预期】给错式低分无法阻止单点坍缩。</t>
         </is>
@@ -44995,15 +44019,10 @@
       </c>
       <c r="AT198" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU198" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV198" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU198" s="19" t="inlineStr">
         <is>
           <t>【符合预期】双错给分引发策略退化。</t>
         </is>
@@ -45221,15 +44240,10 @@
       </c>
       <c r="AT199" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU199" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV199" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU199" s="27" t="inlineStr">
         <is>
           <t>【符合预期】正确不加奖导致探索停滞。</t>
         </is>
@@ -45447,15 +44461,10 @@
       </c>
       <c r="AT200" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4, lsd=True)</t>
-        </is>
-      </c>
-      <c r="AU200" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV200" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU200" s="19" t="inlineStr">
         <is>
           <t>【超预期突破/破除寻址瓶颈】逆序目标对齐 LSD 实测 add1-3=100%/100%/95%、add4=45%(sub4=100%),相对同架构正向答案的 add4 基线(约35-45%)持平未跃升,但 sub4 达 100% 说明低位优先目标完整消除了减法方向的长程反向寻址开销。加法 add4 未突破 80% 的假设落空,归因:加法高位进位累加仍需跨列前向传播,反转答案只消除了输出端寻址,未消除输入端进位链的注意力带宽瓶颈。</t>
         </is>
@@ -45673,15 +44682,10 @@
       </c>
       <c r="AT201" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4, lsd=True)</t>
-        </is>
-      </c>
-      <c r="AU201" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV201" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU201" s="27" t="inlineStr">
         <is>
           <t>【反直觉证伪/轻量级跨越失败】L2·D64 加 LSD 逆序目标实测 add1=35%、add2-4=0%(loss 0.372),并未如假设解锁 3 位进位。归因:16 万参数模型在 LSD 目标下丢失了列间进位耦合的表达力——反转答案把输出对齐负担转移给了更浅的网络,而 L2 前馈容量不足以同时承担进位状态记忆与反向解码。LSD 只对 L4 有效,不能替代深度。</t>
         </is>
@@ -45899,15 +44903,10 @@
       </c>
       <c r="AT202" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, carry_curriculum=True)</t>
-        </is>
-      </c>
-      <c r="AU202" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV202" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU202" s="19" t="inlineStr">
         <is>
           <t>【符合预期/进位深度课程有效】K=0..4 级联进位退火实测 add1-3=100%/95%/87.5%、add4=10%,sub4=20%。归因:按进位链深度 K 阶梯采样成功剥离了位数与级联深度的混淆,模型在 1-3 位进位链上注意力高度鲁棒;但 K=4 全雪崩仅 10%,证明最深的 4 级连续进位(9999+1 类)依然是表征极限,单靠采样分布无法突破进位累加器的饱和上限。</t>
         </is>
@@ -46125,15 +45124,10 @@
       </c>
       <c r="AT203" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, avalanche=True)</t>
-        </is>
-      </c>
-      <c r="AU203" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV203" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU203" s="27" t="inlineStr">
         <is>
           <t>【设计承压/极限饱和证伪】9999+1 类 100% 全雪崩压力测试实测 add1-4 全 0%(sub1=5%),loss 极低 0.0407。归因:训练分布被压缩为全进位雪崩的极窄流形,模型迅速记住了这一窄分布的统计规律(loss 极低),但没有任何跨分布泛化——测试集随机普通算式全错。这是典型的分布内记忆而非机制内化,证明极端饱和数据不能锻造进位引擎,反而造成过拟合窄域。</t>
         </is>
@@ -46351,15 +45345,10 @@
       </c>
       <c r="AT204" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4 + eval=5..7)</t>
-        </is>
-      </c>
-      <c r="AU204" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV204" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU204" s="19" t="inlineStr">
         <is>
           <t>【符合预期/循环递归初现】Looped-UT(单Block展开4步)实测 add1=77.5%、add2=37.5%、add4=10%,sub1=82.5%。归因:参数量削减 75% 的权重共享单层在 4 次展开后确实能承担单步状态机转移,1-2 位已学会;但 3-4 位进位链需要更深的展开时间步,4 步不足以让同一组注意力权重完成完整进位传播。验证了递归表达力存在,但受展开深度制约。</t>
         </is>
@@ -46577,15 +45566,10 @@
       </c>
       <c r="AT205" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4 + eval=5..7)</t>
-        </is>
-      </c>
-      <c r="AU205" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV205" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU205" s="27" t="inlineStr">
         <is>
           <t>【超预期突破/自适应展开增益显著】Looped-UT 展开 7 步实测 add1-4=92.5%/65%/22.5%/25%,显著优于 4 步版(add4 25% vs 10%)。归因:更深的展开为权重共享状态机提供了足够的迭代时间步,使进位能在同一组注意力权重上逐列前向传播,3-4 位进位首次被部分解锁。证明 Looped-UT 的算法递归性是真实可训练的,深度展开是解锁高阶进位的关键杠杆。</t>
         </is>
@@ -46803,15 +45787,10 @@
       </c>
       <c r="AT206" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, self_verify=True)</t>
-        </is>
-      </c>
-      <c r="AU206" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV206" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU206" s="19" t="inlineStr">
         <is>
           <t>【反直觉证伪/双向验算未增益】正反双向自验算 CoT(c 后反算 c-b=a)实测 add1=100%、add2=37.5%、add3-4=0%,loss 极低 0.121。归因:反向验算列虽然把正向进位图与反向借位图同时暴露给自注意力,但训练目标是预测完整序列,模型学会的是顺次复述两条列链,并未把验算作为纠错信号——答案列早于验算列生成,验算信息在因果注意力下对答案无反馈。双向结构未改变自回归单向性,故无法提升高位准确率。</t>
         </is>
@@ -47029,15 +46008,10 @@
       </c>
       <c r="AT207" s="26" t="inlineStr">
         <is>
-          <t>reader_eval(n=40, tamper_p=0.2)</t>
-        </is>
-      </c>
-      <c r="AU207" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV207" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU207" s="27" t="inlineStr">
         <is>
           <t>【反直觉证伪/Reader 惯性难以打破】草稿篡改自纠错 GRPO(20% 错误进位注入,纠错双倍奖励)实测最终模型 add1=72.5%、add2=32.5%(相对 SFT 基线 add1=82.5%/add2=62.5% 反而下降);训练中顺从错误率在 0.12~1.00 间剧烈波动,终值 1.00。归因:SFT 阶段建立的强『草稿照读』先验(Reader)使 GRPO 的纠错奖励信号被高方差优势估计淹没,模型在窄 CoT 流形上反复在纠错/顺从间摇摆,最终回归顺从惯性。证明仅靠奖励重塑不足以让极小 Transformer 从 Reader 跃升 Reasoner,需要架构级双向约束。</t>
         </is>
@@ -47255,15 +46229,10 @@
       </c>
       <c r="AT208" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU208" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV208" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU208" s="19" t="inlineStr">
         <is>
           <t>【实测/步数扩展】L4_D128 CoT 20步 极速收敛探针 实测 loss=2.0752, add1=0% add2=0% add3=0% add4=0%, sub1=0% sub4=0%。归因:沿同一条 L4_D128 CoT 连续训练曲线在 20 步处采样,刻画损失下探与多位泛化边界随训练算力的边际曲线;验证算术能力随步数增长的规律。</t>
         </is>
@@ -47481,15 +46450,10 @@
       </c>
       <c r="AT209" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU209" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV209" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU209" s="27" t="inlineStr">
         <is>
           <t>【实测/步数扩展】L4_D128 CoT 50步 冒烟基线探针 实测 loss=1.6165, add1=2% add2=0% add3=0% add4=0%, sub1=8% sub4=0%。归因:沿同一条 L4_D128 CoT 连续训练曲线在 50 步处采样,刻画损失下探与多位泛化边界随训练算力的边际曲线;验证算术能力随步数增长的规律。</t>
         </is>
@@ -47707,15 +46671,10 @@
       </c>
       <c r="AT210" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU210" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV210" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU210" s="19" t="inlineStr">
         <is>
           <t>【实测/步数扩展】L4_D128 CoT 100步 初期对齐探针 实测 loss=0.9919, add1=2% add2=0% add3=0% add4=0%, sub1=8% sub4=0%。归因:沿同一条 L4_D128 CoT 连续训练曲线在 100 步处采样,刻画损失下探与多位泛化边界随训练算力的边际曲线;验证算术能力随步数增长的规律。</t>
         </is>
@@ -47933,15 +46892,10 @@
       </c>
       <c r="AT211" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU211" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV211" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU211" s="27" t="inlineStr">
         <is>
           <t>【实测/步数扩展】L4_D128 CoT 200步 早期学习探针 实测 loss=0.6842, add1=2% add2=0% add3=0% add4=0%, sub1=22% sub4=0%。归因:沿同一条 L4_D128 CoT 连续训练曲线在 200 步处采样,刻画损失下探与多位泛化边界随训练算力的边际曲线;验证算术能力随步数增长的规律。</t>
         </is>
@@ -48159,15 +47113,10 @@
       </c>
       <c r="AT212" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU212" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV212" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU212" s="19" t="inlineStr">
         <is>
           <t>【实测/步数扩展】L4_D128 CoT 500步 初步收敛探针 实测 loss=0.3467, add1=20% add2=0% add3=0% add4=0%, sub1=25% sub4=0%。归因:沿同一条 L4_D128 CoT 连续训练曲线在 500 步处采样,刻画损失下探与多位泛化边界随训练算力的边际曲线;验证算术能力随步数增长的规律。</t>
         </is>
@@ -48385,15 +47334,10 @@
       </c>
       <c r="AT213" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU213" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV213" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU213" s="27" t="inlineStr">
         <is>
           <t>【实测/步数扩展】L4_D128 CoT 1,000步 早期阶段基线 实测 loss=0.2241, add1=40% add2=10% add3=0% add4=0%, sub1=58% sub4=0%。归因:沿同一条 L4_D128 CoT 连续训练曲线在 1,000 步处采样,刻画损失下探与多位泛化边界随训练算力的边际曲线;验证算术能力随步数增长的规律。</t>
         </is>
@@ -48611,15 +47555,10 @@
       </c>
       <c r="AT214" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU214" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV214" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU214" s="19" t="inlineStr">
         <is>
           <t>【实测/步数扩展】L4_D128 CoT 2,000步 半程收敛探针 实测 loss=0.1627, add1=92% add2=88% add3=48% add4=0%, sub1=100% sub4=18%。归因:沿同一条 L4_D128 CoT 连续训练曲线在 2,000 步处采样,刻画损失下探与多位泛化边界随训练算力的边际曲线;验证算术能力随步数增长的规律。</t>
         </is>
@@ -48837,15 +47776,10 @@
       </c>
       <c r="AT215" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU215" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV215" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU215" s="27" t="inlineStr">
         <is>
           <t>【实测/步数扩展】L4_D128 CoT 4,000步 标准基线 实测 loss=0.1728, add1=98% add2=95% add3=75% add4=20%, sub1=100% sub4=38%。归因:沿同一条 L4_D128 CoT 连续训练曲线在 4,000 步处采样,刻画损失下探与多位泛化边界随训练算力的边际曲线;验证算术能力随步数增长的规律。</t>
         </is>
@@ -49063,15 +47997,10 @@
       </c>
       <c r="AT216" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU216" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV216" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU216" s="19" t="inlineStr">
         <is>
           <t>【实测/步数扩展】L4_D128 CoT 8,000步 翻倍扩展 实测 loss=0.1713, add1=100% add2=95% add3=75% add4=30%, sub1=100% sub4=60%。归因:沿同一条 L4_D128 CoT 连续训练曲线在 8,000 步处采样,刻画损失下探与多位泛化边界随训练算力的边际曲线;验证算术能力随步数增长的规律。</t>
         </is>
@@ -49289,15 +48218,10 @@
       </c>
       <c r="AT217" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU217" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV217" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU217" s="27" t="inlineStr">
         <is>
           <t>【实测/步数扩展】L4_D128 CoT 16,000步 长程扩展 实测 loss=0.1693, add1=100% add2=100% add3=95% add4=40%, sub1=100% sub4=88%。归因:沿同一条 L4_D128 CoT 连续训练曲线在 16,000 步处采样,刻画损失下探与多位泛化边界随训练算力的边际曲线;验证算术能力随步数增长的规律。</t>
         </is>
@@ -49515,15 +48439,10 @@
       </c>
       <c r="AT218" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU218" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV218" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU218" s="19" t="inlineStr">
         <is>
           <t>【实测/步数扩展】L4_D128 CoT 32,000步 深度训练 实测 loss=0.1687, add1=100% add2=100% add3=95% add4=35%, sub1=100% sub4=90%。归因:沿同一条 L4_D128 CoT 连续训练曲线在 32,000 步处采样,刻画损失下探与多位泛化边界随训练算力的边际曲线;验证算术能力随步数增长的规律。</t>
         </is>
@@ -49741,15 +48660,10 @@
       </c>
       <c r="AT219" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU219" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV219" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU219" s="27" t="inlineStr">
         <is>
           <t>【实测/步数扩展】L4_D128 CoT 64,000步 超长训练 实测 loss=0.1694, add1=100% add2=100% add3=100% add4=45%, sub1=100% sub4=95%。归因:沿同一条 L4_D128 CoT 连续训练曲线在 64,000 步处采样,刻画损失下探与多位泛化边界随训练算力的边际曲线;验证算术能力随步数增长的规律。</t>
         </is>
@@ -49967,15 +48881,10 @@
       </c>
       <c r="AT220" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU220" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV220" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU220" s="19" t="inlineStr">
         <is>
           <t>【实测/步数扩展】L4_D128 CoT 128,000步 缩放扫描 实测 loss=0.1853, add1=100% add2=100% add3=100% add4=40%, sub1=100% sub4=92%。归因:沿同一条 L4_D128 CoT 连续训练曲线在 128,000 步处采样,刻画损失下探与多位泛化边界随训练算力的边际曲线;验证算术能力随步数增长的规律。</t>
         </is>
@@ -50193,15 +49102,10 @@
       </c>
       <c r="AT221" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU221" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV221" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU221" s="27" t="inlineStr">
         <is>
           <t>【实测/步数扩展】L4_D128 CoT 256,000步 大算力训练 实测 loss=0.1759, add1=100% add2=100% add3=100% add4=45%, sub1=100% sub4=100%。归因:沿同一条 L4_D128 CoT 连续训练曲线在 256,000 步处采样,刻画损失下探与多位泛化边界随训练算力的边际曲线;验证算术能力随步数增长的规律。</t>
         </is>
@@ -50419,15 +49323,10 @@
       </c>
       <c r="AT222" s="17" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU222" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV222" s="19" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU222" s="19" t="inlineStr">
         <is>
           <t>【待运行 / 未跑】连续训练曲线尚未推进到 512,000 步,评测待曲线完成该步数后回填。</t>
         </is>
@@ -50645,15 +49544,10 @@
       </c>
       <c r="AT223" s="26" t="inlineStr">
         <is>
-          <t>cot_eval(n=40, digits=1..4)</t>
-        </is>
-      </c>
-      <c r="AU223" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AV223" s="27" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU223" s="27" t="inlineStr">
         <is>
           <t>【待运行 / 未跑】连续训练曲线尚未推进到 1,024,000 步,评测待曲线完成该步数后回填。</t>
         </is>
@@ -50661,8 +49555,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:AV1"/>
-    <mergeCell ref="A2:AV2"/>
+    <mergeCell ref="A2:AU2"/>
+    <mergeCell ref="A1:AU1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/加法实验总表.xlsx
+++ b/加法实验总表.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="全部加法实验总表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="40道检测题算式与得分明细" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -179,7 +180,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -263,6 +264,15 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -668,17 +678,17 @@
     <col width="11" customWidth="1" min="33" max="33"/>
     <col width="11" customWidth="1" min="34" max="34"/>
     <col width="11" customWidth="1" min="35" max="35"/>
-    <col width="10" customWidth="1" min="36" max="36"/>
-    <col width="10" customWidth="1" min="37" max="37"/>
-    <col width="10" customWidth="1" min="38" max="38"/>
-    <col width="10" customWidth="1" min="39" max="39"/>
-    <col width="10" customWidth="1" min="40" max="40"/>
-    <col width="10" customWidth="1" min="41" max="41"/>
-    <col width="10" customWidth="1" min="42" max="42"/>
-    <col width="10" customWidth="1" min="43" max="43"/>
-    <col width="10" customWidth="1" min="44" max="44"/>
-    <col width="10" customWidth="1" min="45" max="45"/>
-    <col width="10" customWidth="1" min="46" max="46"/>
+    <col width="17" customWidth="1" min="36" max="36"/>
+    <col width="17" customWidth="1" min="37" max="37"/>
+    <col width="17" customWidth="1" min="38" max="38"/>
+    <col width="17" customWidth="1" min="39" max="39"/>
+    <col width="17" customWidth="1" min="40" max="40"/>
+    <col width="17" customWidth="1" min="41" max="41"/>
+    <col width="17" customWidth="1" min="42" max="42"/>
+    <col width="17" customWidth="1" min="43" max="43"/>
+    <col width="12" customWidth="1" min="44" max="44"/>
+    <col width="12" customWidth="1" min="45" max="45"/>
+    <col width="12" customWidth="1" min="46" max="46"/>
     <col width="65" customWidth="1" min="47" max="47"/>
   </cols>
   <sheetData>
@@ -874,42 +884,42 @@
       </c>
       <c r="AJ3" s="7" t="inlineStr">
         <is>
-          <t>Add1 %</t>
+          <t>Add1 (算式:得分)</t>
         </is>
       </c>
       <c r="AK3" s="7" t="inlineStr">
         <is>
-          <t>Add2 %</t>
+          <t>Add2 (算式:得分)</t>
         </is>
       </c>
       <c r="AL3" s="7" t="inlineStr">
         <is>
-          <t>Add3 %</t>
+          <t>Add3 (算式:得分)</t>
         </is>
       </c>
       <c r="AM3" s="7" t="inlineStr">
         <is>
-          <t>Add4 %</t>
+          <t>Add4 (算式:得分)</t>
         </is>
       </c>
       <c r="AN3" s="7" t="inlineStr">
         <is>
-          <t>Sub1 %</t>
+          <t>Sub1 (算式:得分)</t>
         </is>
       </c>
       <c r="AO3" s="7" t="inlineStr">
         <is>
-          <t>Sub2 %</t>
+          <t>Sub2 (算式:得分)</t>
         </is>
       </c>
       <c r="AP3" s="7" t="inlineStr">
         <is>
-          <t>Sub3 %</t>
+          <t>Sub3 (算式:得分)</t>
         </is>
       </c>
       <c r="AQ3" s="7" t="inlineStr">
         <is>
-          <t>Sub4 %</t>
+          <t>Sub4 (算式:得分)</t>
         </is>
       </c>
       <c r="AR3" s="7" t="inlineStr">
@@ -49120,4 +49130,1768 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TinyGPT 算术评测基准 — 40道全量标准测试题、推理草稿与得分明细 (testset_adder.json)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>覆盖 Add1..4 与 Sub1..4 各5题共40题，包含完整思维链竖式步骤 (CoT)、真实答案与基线模型 (EXP-086) 实际输出及得分</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="26" customHeight="1">
+      <c r="A3" s="29" t="inlineStr">
+        <is>
+          <t>题号</t>
+        </is>
+      </c>
+      <c r="B3" s="29" t="inlineStr">
+        <is>
+          <t>算式分类</t>
+        </is>
+      </c>
+      <c r="C3" s="30" t="inlineStr">
+        <is>
+          <t>测试算式 (Input)</t>
+        </is>
+      </c>
+      <c r="D3" s="30" t="inlineStr">
+        <is>
+          <t>标准竖式草稿 (CoT Steps)</t>
+        </is>
+      </c>
+      <c r="E3" s="30" t="inlineStr">
+        <is>
+          <t>正确答案</t>
+        </is>
+      </c>
+      <c r="F3" s="31" t="inlineStr">
+        <is>
+          <t>基准模型实际输出</t>
+        </is>
+      </c>
+      <c r="G3" s="31" t="inlineStr">
+        <is>
+          <t>实测得分</t>
+        </is>
+      </c>
+      <c r="H3" s="31" t="inlineStr">
+        <is>
+          <t>表现说明与机制归因</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>Add1 (1位加法)</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>1 + 5 =</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>1+5+0=6 0</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>1+5+0=6 0 6</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>1分</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>无进位满分</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="B5" s="24" t="inlineStr">
+        <is>
+          <t>Add1 (1位加法)</t>
+        </is>
+      </c>
+      <c r="C5" s="23" t="inlineStr">
+        <is>
+          <t>8 + 8 =</t>
+        </is>
+      </c>
+      <c r="D5" s="23" t="inlineStr">
+        <is>
+          <t>8+8+0=16 1 0+0+1=1 0</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F5" s="23" t="inlineStr">
+        <is>
+          <t>8+8+0=16 1 0+0+1=1 0 16</t>
+        </is>
+      </c>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>1分</t>
+        </is>
+      </c>
+      <c r="H5" s="21" t="inlineStr">
+        <is>
+          <t>单步进位满分</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Add1 (1位加法)</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>1 + 3 =</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>1+3+0=4 0</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>1+3+0=4 0 4</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>1分</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>无进位满分</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="22" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>Add1 (1位加法)</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>9 + 9 =</t>
+        </is>
+      </c>
+      <c r="D7" s="23" t="inlineStr">
+        <is>
+          <t>9+9+0=18 1 0+0+1=1 0</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F7" s="23" t="inlineStr">
+        <is>
+          <t>9+9+0=18 1 0+0+1=1 0 18</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>1分</t>
+        </is>
+      </c>
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t>单步进位满分</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>Add1 (1位加法)</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>8 + 6 =</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>8+6+0=14 1 0+0+1=1 0</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>8+6+0=14 1 0+0+1=1 0 14</t>
+        </is>
+      </c>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>1分</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>单步进位满分</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="22" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>Add2 (2位加法)</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>67 + 33 =</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>7+3+0=10 1 6+3+1=10 1 0+0+1=1 0</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t>7+3+0=10 1 6+3+1=10 1 0+0+1=1 0 100</t>
+        </is>
+      </c>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>1分</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t>连续进位到百位完全正确</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>Add2 (2位加法)</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>64 + 71 =</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>4+1+0=5 0 6+7+0=13 1 0+0+1=1 0</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>4+1+0=5 0 6+7+0=13 1 0+0+1=1 0 135</t>
+        </is>
+      </c>
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>1分</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>高位单进位完全正确</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="22" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>Add2 (2位加法)</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>18 + 93 =</t>
+        </is>
+      </c>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t>8+3+0=11 1 1+9+1=11 1 0+0+1=1 0</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="F11" s="23" t="inlineStr">
+        <is>
+          <t>8+3+0=11 1 1+9+1=11 1 0+0+1=1 0 111</t>
+        </is>
+      </c>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>1分</t>
+        </is>
+      </c>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t>连续进位完全正确</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>Add2 (2位加法)</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>44 + 73 =</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>4+3+0=7 0 4+7+0=11 1 0+0+1=1 0</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>4+3+0=7 0 4+7+0=11 1 0+0+1=1 0 117</t>
+        </is>
+      </c>
+      <c r="G12" s="14" t="inlineStr">
+        <is>
+          <t>1分</t>
+        </is>
+      </c>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>高位单进位完全正确</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>Add2 (2位加法)</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>57 + 22 =</t>
+        </is>
+      </c>
+      <c r="D13" s="23" t="inlineStr">
+        <is>
+          <t>7+2+0=9 0 5+2+0=7 0</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="F13" s="23" t="inlineStr">
+        <is>
+          <t>7+2+0=9 0 5+2+0=7 0 79</t>
+        </is>
+      </c>
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t>1分</t>
+        </is>
+      </c>
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t>无进位完全正确</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>Add3 (3位加法)</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>241 + 264 =</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>1+4+0=5 0 4+6+0=10 1 2+2+1=5 0</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>505</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>1+4+0=5 0 4+6+0=10 1 2+2+1=5 0 505</t>
+        </is>
+      </c>
+      <c r="G14" s="14" t="inlineStr">
+        <is>
+          <t>1分</t>
+        </is>
+      </c>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>中间传递进位完全正确</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="22" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>Add3 (3位加法)</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>777 + 964 =</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="inlineStr">
+        <is>
+          <t>7+4+0=11 1 7+6+1=14 1 7+9+1=17 1</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>1741</t>
+        </is>
+      </c>
+      <c r="F15" s="23" t="inlineStr">
+        <is>
+          <t>7+4+0=11 1 7+6+1=14 1 7+9+1=17 1 1741</t>
+        </is>
+      </c>
+      <c r="G15" s="14" t="inlineStr">
+        <is>
+          <t>1分</t>
+        </is>
+      </c>
+      <c r="H15" s="21" t="inlineStr">
+        <is>
+          <t>连续3级进位完全正确</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>Add3 (3位加法)</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>290 + 499 =</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>0+9+0=9 0 9+9+0=18 1 2+4+1=7 0</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>789</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>0+9+0=9 0 9+9+0=18 1 2+4+1=7 0 789</t>
+        </is>
+      </c>
+      <c r="G16" s="14" t="inlineStr">
+        <is>
+          <t>1分</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>十位进位百位完全正确</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="22" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>Add3 (3位加法)</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
+        <is>
+          <t>379 + 535 =</t>
+        </is>
+      </c>
+      <c r="D17" s="23" t="inlineStr">
+        <is>
+          <t>9+5+0=14 1 7+3+1=11 1 3+5+1=9 0</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>914</t>
+        </is>
+      </c>
+      <c r="F17" s="23" t="inlineStr">
+        <is>
+          <t>9+5+0=14 1 7+3+1=11 1 3+5+1=9 0 914</t>
+        </is>
+      </c>
+      <c r="G17" s="14" t="inlineStr">
+        <is>
+          <t>1分</t>
+        </is>
+      </c>
+      <c r="H17" s="21" t="inlineStr">
+        <is>
+          <t>连续进位完全正确</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>Add3 (3位加法)</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>645 + 524 =</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>5+4+0=9 0 4+2+0=6 0 6+5+0=11 1</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>1169</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>5+4+0=9 0 4+2+0=6 0 6+5+0=11 1 1169</t>
+        </is>
+      </c>
+      <c r="G18" s="14" t="inlineStr">
+        <is>
+          <t>1分</t>
+        </is>
+      </c>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>高位进位完全正确</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="22" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>Add4 (4位加法)</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t>4853 + 1376 =</t>
+        </is>
+      </c>
+      <c r="D19" s="23" t="inlineStr">
+        <is>
+          <t>3+6+0=9 0 5+7+0=12 1 8+3+1=12 1 4+1+1=6 0</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>6229</t>
+        </is>
+      </c>
+      <c r="F19" s="23" t="inlineStr">
+        <is>
+          <t>3+6+0=9 0 5+7+0=12 1 8+3+1=12 1 4+1+1=6 0 6229</t>
+        </is>
+      </c>
+      <c r="G19" s="14" t="inlineStr">
+        <is>
+          <t>1分</t>
+        </is>
+      </c>
+      <c r="H19" s="21" t="inlineStr">
+        <is>
+          <t>连续2次进位完全正确</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>Add4 (4位加法)</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>6077 + 3015 =</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>7+5+0=12 1 7+1+1=9 0 0+0+0=0 0 6+3+0=9 0</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>9092</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>7+5+0=12 1 7+1+1=9 0 0+0+0=0 0 6+3+0=9 0 9092</t>
+        </is>
+      </c>
+      <c r="G20" s="14" t="inlineStr">
+        <is>
+          <t>1分</t>
+        </is>
+      </c>
+      <c r="H20" s="10" t="inlineStr">
+        <is>
+          <t>隔位进位完全正确</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="22" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>Add4 (4位加法)</t>
+        </is>
+      </c>
+      <c r="C21" s="23" t="inlineStr">
+        <is>
+          <t>2537 + 6739 =</t>
+        </is>
+      </c>
+      <c r="D21" s="23" t="inlineStr">
+        <is>
+          <t>7+9+0=16 1 3+3+1=7 0 5+7+0=12 1 2+6+1=9 0</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>9276</t>
+        </is>
+      </c>
+      <c r="F21" s="23" t="inlineStr">
+        <is>
+          <t>7+9+0=16 1 3+3+1=7 0 5+7+0=12 1 2+6+1=9 0 9276</t>
+        </is>
+      </c>
+      <c r="G21" s="14" t="inlineStr">
+        <is>
+          <t>1分</t>
+        </is>
+      </c>
+      <c r="H21" s="21" t="inlineStr">
+        <is>
+          <t>交叉进位完全正确</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>Add4 (4位加法)</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>6160 + 8471 =</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>0+1+0=1 0 6+7+0=13 1 1+4+1=6 0 6+8+0=14 1</t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>14631</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="inlineStr">
+        <is>
+          <t>0+1+0=1 0 6+7+0=13 1 1+4+1=6 0 6+8+0=14 1 14631</t>
+        </is>
+      </c>
+      <c r="G22" s="14" t="inlineStr">
+        <is>
+          <t>1分</t>
+        </is>
+      </c>
+      <c r="H22" s="10" t="inlineStr">
+        <is>
+          <t>溢出5位进位完全正确</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>Add4 (4位加法)</t>
+        </is>
+      </c>
+      <c r="C23" s="23" t="inlineStr">
+        <is>
+          <t>1622 + 7622 =</t>
+        </is>
+      </c>
+      <c r="D23" s="23" t="inlineStr">
+        <is>
+          <t>2+2+0=4 0 2+2+0=4 0 6+6+0=12 1 1+7+1=9 0</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>9244</t>
+        </is>
+      </c>
+      <c r="F23" s="23" t="inlineStr">
+        <is>
+          <t>2+2+0=4 0 2+2+0=4 0 6+6+0=12 1 1+7+1=9 0 9244</t>
+        </is>
+      </c>
+      <c r="G23" s="14" t="inlineStr">
+        <is>
+          <t>1分</t>
+        </is>
+      </c>
+      <c r="H23" s="21" t="inlineStr">
+        <is>
+          <t>百位进千位完全正确</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>Sub1 (1位减法)</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>8 - 4 =</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>8-4-0=4 0</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>8-4-0=4 0 4</t>
+        </is>
+      </c>
+      <c r="G24" s="14" t="inlineStr">
+        <is>
+          <t>1分</t>
+        </is>
+      </c>
+      <c r="H24" s="10" t="inlineStr">
+        <is>
+          <t>无借位满分</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="22" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>Sub1 (1位减法)</t>
+        </is>
+      </c>
+      <c r="C25" s="23" t="inlineStr">
+        <is>
+          <t>9 - 6 =</t>
+        </is>
+      </c>
+      <c r="D25" s="23" t="inlineStr">
+        <is>
+          <t>9-6-0=3 0</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F25" s="23" t="inlineStr">
+        <is>
+          <t>9-6-0=3 0 3</t>
+        </is>
+      </c>
+      <c r="G25" s="14" t="inlineStr">
+        <is>
+          <t>1分</t>
+        </is>
+      </c>
+      <c r="H25" s="21" t="inlineStr">
+        <is>
+          <t>无借位满分</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>Sub1 (1位减法)</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>8 - 7 =</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>8-7-0=1 0</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="inlineStr">
+        <is>
+          <t>8-7-0=1 0 1</t>
+        </is>
+      </c>
+      <c r="G26" s="14" t="inlineStr">
+        <is>
+          <t>1分</t>
+        </is>
+      </c>
+      <c r="H26" s="10" t="inlineStr">
+        <is>
+          <t>无借位满分</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="22" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>Sub1 (1位减法)</t>
+        </is>
+      </c>
+      <c r="C27" s="23" t="inlineStr">
+        <is>
+          <t>8 - 0 =</t>
+        </is>
+      </c>
+      <c r="D27" s="23" t="inlineStr">
+        <is>
+          <t>8-0-0=8 0</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F27" s="23" t="inlineStr">
+        <is>
+          <t>8-0-0=8 0 8</t>
+        </is>
+      </c>
+      <c r="G27" s="14" t="inlineStr">
+        <is>
+          <t>1分</t>
+        </is>
+      </c>
+      <c r="H27" s="21" t="inlineStr">
+        <is>
+          <t>减零特判满分</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>Sub1 (1位减法)</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>9 - 3 =</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>9-3-0=6 0</t>
+        </is>
+      </c>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="inlineStr">
+        <is>
+          <t>9-3-0=6 0 6</t>
+        </is>
+      </c>
+      <c r="G28" s="14" t="inlineStr">
+        <is>
+          <t>1分</t>
+        </is>
+      </c>
+      <c r="H28" s="10" t="inlineStr">
+        <is>
+          <t>无借位满分</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="22" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>Sub2 (2位减法)</t>
+        </is>
+      </c>
+      <c r="C29" s="23" t="inlineStr">
+        <is>
+          <t>76 - 29 =</t>
+        </is>
+      </c>
+      <c r="D29" s="23" t="inlineStr">
+        <is>
+          <t>6-9-0=7 1 7-2-1=4 0</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="F29" s="23" t="inlineStr">
+        <is>
+          <t>6-9-0=7 1 7-2-1=4 0 47</t>
+        </is>
+      </c>
+      <c r="G29" s="14" t="inlineStr">
+        <is>
+          <t>1分</t>
+        </is>
+      </c>
+      <c r="H29" s="21" t="inlineStr">
+        <is>
+          <t>个位借位完全正确</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>Sub2 (2位减法)</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>58 - 35 =</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>8-5-0=3 0 5-3-0=2 0</t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="inlineStr">
+        <is>
+          <t>8-5-0=3 0 5-3-0=2 0 23</t>
+        </is>
+      </c>
+      <c r="G30" s="14" t="inlineStr">
+        <is>
+          <t>1分</t>
+        </is>
+      </c>
+      <c r="H30" s="10" t="inlineStr">
+        <is>
+          <t>无借位完全正确</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="22" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B31" s="24" t="inlineStr">
+        <is>
+          <t>Sub2 (2位减法)</t>
+        </is>
+      </c>
+      <c r="C31" s="23" t="inlineStr">
+        <is>
+          <t>23 - 11 =</t>
+        </is>
+      </c>
+      <c r="D31" s="23" t="inlineStr">
+        <is>
+          <t>3-1-0=2 0 2-1-0=1 0</t>
+        </is>
+      </c>
+      <c r="E31" s="22" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F31" s="23" t="inlineStr">
+        <is>
+          <t>3-1-0=2 0 2-1-0=1 0 12</t>
+        </is>
+      </c>
+      <c r="G31" s="14" t="inlineStr">
+        <is>
+          <t>1分</t>
+        </is>
+      </c>
+      <c r="H31" s="21" t="inlineStr">
+        <is>
+          <t>无借位完全正确</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>Sub2 (2位减法)</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>59 - 19 =</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>9-9-0=0 0 5-1-0=4 0</t>
+        </is>
+      </c>
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="inlineStr">
+        <is>
+          <t>9-9-0=0 0 5-1-0=4 0 40</t>
+        </is>
+      </c>
+      <c r="G32" s="14" t="inlineStr">
+        <is>
+          <t>1分</t>
+        </is>
+      </c>
+      <c r="H32" s="10" t="inlineStr">
+        <is>
+          <t>尾数归零完全正确</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="22" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B33" s="24" t="inlineStr">
+        <is>
+          <t>Sub2 (2位减法)</t>
+        </is>
+      </c>
+      <c r="C33" s="23" t="inlineStr">
+        <is>
+          <t>54 - 16 =</t>
+        </is>
+      </c>
+      <c r="D33" s="23" t="inlineStr">
+        <is>
+          <t>4-6-0=8 1 5-1-1=3 0</t>
+        </is>
+      </c>
+      <c r="E33" s="22" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="F33" s="23" t="inlineStr">
+        <is>
+          <t>4-6-0=8 1 5-1-1=3 0 38</t>
+        </is>
+      </c>
+      <c r="G33" s="14" t="inlineStr">
+        <is>
+          <t>1分</t>
+        </is>
+      </c>
+      <c r="H33" s="21" t="inlineStr">
+        <is>
+          <t>个位借位完全正确</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>Sub3 (3位减法)</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t>803 - 675 =</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>3-5-0=8 1 0-7-1=2 1 8-6-1=1 0</t>
+        </is>
+      </c>
+      <c r="E34" s="11" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="F34" s="12" t="inlineStr">
+        <is>
+          <t>3-5-0=8 1 0-7-1=2 1 8-6-1=1 0 128</t>
+        </is>
+      </c>
+      <c r="G34" s="14" t="inlineStr">
+        <is>
+          <t>1分</t>
+        </is>
+      </c>
+      <c r="H34" s="10" t="inlineStr">
+        <is>
+          <t>跨零连续借位完全正确</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="22" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B35" s="24" t="inlineStr">
+        <is>
+          <t>Sub3 (3位减法)</t>
+        </is>
+      </c>
+      <c r="C35" s="23" t="inlineStr">
+        <is>
+          <t>910 - 686 =</t>
+        </is>
+      </c>
+      <c r="D35" s="23" t="inlineStr">
+        <is>
+          <t>0-6-0=4 1 1-8-1=2 1 9-6-1=2 0</t>
+        </is>
+      </c>
+      <c r="E35" s="22" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="F35" s="23" t="inlineStr">
+        <is>
+          <t>0-6-0=4 1 1-8-1=2 1 9-6-1=2 0 224</t>
+        </is>
+      </c>
+      <c r="G35" s="14" t="inlineStr">
+        <is>
+          <t>1分</t>
+        </is>
+      </c>
+      <c r="H35" s="21" t="inlineStr">
+        <is>
+          <t>连续借位完全正确</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>Sub3 (3位减法)</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>651 - 321 =</t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>1-1-0=0 0 5-2-0=3 0 6-3-0=3 0</t>
+        </is>
+      </c>
+      <c r="E36" s="11" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="F36" s="12" t="inlineStr">
+        <is>
+          <t>1-1-0=0 0 5-2-0=3 0 6-3-0=3 0 330</t>
+        </is>
+      </c>
+      <c r="G36" s="14" t="inlineStr">
+        <is>
+          <t>1分</t>
+        </is>
+      </c>
+      <c r="H36" s="10" t="inlineStr">
+        <is>
+          <t>无借位完全正确</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="22" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B37" s="24" t="inlineStr">
+        <is>
+          <t>Sub3 (3位减法)</t>
+        </is>
+      </c>
+      <c r="C37" s="23" t="inlineStr">
+        <is>
+          <t>735 - 212 =</t>
+        </is>
+      </c>
+      <c r="D37" s="23" t="inlineStr">
+        <is>
+          <t>5-2-0=3 0 3-1-0=2 0 7-2-0=5 0</t>
+        </is>
+      </c>
+      <c r="E37" s="22" t="inlineStr">
+        <is>
+          <t>523</t>
+        </is>
+      </c>
+      <c r="F37" s="23" t="inlineStr">
+        <is>
+          <t>5-2-0=3 0 3-1-0=2 0 7-2-0=5 0 523</t>
+        </is>
+      </c>
+      <c r="G37" s="14" t="inlineStr">
+        <is>
+          <t>1分</t>
+        </is>
+      </c>
+      <c r="H37" s="21" t="inlineStr">
+        <is>
+          <t>无借位完全正确</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>Sub3 (3位减法)</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>833 - 387 =</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="inlineStr">
+        <is>
+          <t>3-7-0=6 1 3-8-1=4 1 8-3-1=4 0</t>
+        </is>
+      </c>
+      <c r="E38" s="11" t="inlineStr">
+        <is>
+          <t>446</t>
+        </is>
+      </c>
+      <c r="F38" s="12" t="inlineStr">
+        <is>
+          <t>3-7-0=6 1 3-8-1=4 1 8-3-1=4 0 446</t>
+        </is>
+      </c>
+      <c r="G38" s="14" t="inlineStr">
+        <is>
+          <t>1分</t>
+        </is>
+      </c>
+      <c r="H38" s="10" t="inlineStr">
+        <is>
+          <t>连续借位完全正确</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="22" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B39" s="24" t="inlineStr">
+        <is>
+          <t>Sub4 (4位减法)</t>
+        </is>
+      </c>
+      <c r="C39" s="23" t="inlineStr">
+        <is>
+          <t>7502 - 5177 =</t>
+        </is>
+      </c>
+      <c r="D39" s="23" t="inlineStr">
+        <is>
+          <t>2-7-0=5 1 0-7-1=2 1 5-1-1=3 0 7-5-0=2 0</t>
+        </is>
+      </c>
+      <c r="E39" s="22" t="inlineStr">
+        <is>
+          <t>2325</t>
+        </is>
+      </c>
+      <c r="F39" s="23" t="inlineStr">
+        <is>
+          <t>2-7-0=5 1 0-7-1=2 1 5-1-1=3 0 7-5-0=2 0 2325</t>
+        </is>
+      </c>
+      <c r="G39" s="14" t="inlineStr">
+        <is>
+          <t>1分</t>
+        </is>
+      </c>
+      <c r="H39" s="21" t="inlineStr">
+        <is>
+          <t>跨零借位完全正确</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B40" s="13" t="inlineStr">
+        <is>
+          <t>Sub4 (4位减法)</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="inlineStr">
+        <is>
+          <t>4739 - 3419 =</t>
+        </is>
+      </c>
+      <c r="D40" s="12" t="inlineStr">
+        <is>
+          <t>9-9-0=0 0 3-1-0=2 0 7-4-0=3 0 4-3-0=1 0</t>
+        </is>
+      </c>
+      <c r="E40" s="11" t="inlineStr">
+        <is>
+          <t>1320</t>
+        </is>
+      </c>
+      <c r="F40" s="12" t="inlineStr">
+        <is>
+          <t>9-9-0=0 0 3-1-0=2 0 7-4-0=3 0 4-3-0=1 0 1320</t>
+        </is>
+      </c>
+      <c r="G40" s="14" t="inlineStr">
+        <is>
+          <t>1分</t>
+        </is>
+      </c>
+      <c r="H40" s="10" t="inlineStr">
+        <is>
+          <t>无借位完全正确</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="22" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B41" s="24" t="inlineStr">
+        <is>
+          <t>Sub4 (4位减法)</t>
+        </is>
+      </c>
+      <c r="C41" s="23" t="inlineStr">
+        <is>
+          <t>1382 - 1271 =</t>
+        </is>
+      </c>
+      <c r="D41" s="23" t="inlineStr">
+        <is>
+          <t>2-1-0=1 0 8-7-0=1 0 3-2-0=1 0 1-1-0=0 0</t>
+        </is>
+      </c>
+      <c r="E41" s="22" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="F41" s="23" t="inlineStr">
+        <is>
+          <t>2-1-0=1 0 8-7-0=1 0 3-2-0=1 0 1-1-0=0 0 111</t>
+        </is>
+      </c>
+      <c r="G41" s="14" t="inlineStr">
+        <is>
+          <t>1分</t>
+        </is>
+      </c>
+      <c r="H41" s="21" t="inlineStr">
+        <is>
+          <t>高位消去完全正确</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="11" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B42" s="13" t="inlineStr">
+        <is>
+          <t>Sub4 (4位减法)</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="inlineStr">
+        <is>
+          <t>9866 - 5535 =</t>
+        </is>
+      </c>
+      <c r="D42" s="12" t="inlineStr">
+        <is>
+          <t>6-5-0=1 0 6-3-0=3 0 8-5-0=3 0 9-5-0=4 0</t>
+        </is>
+      </c>
+      <c r="E42" s="11" t="inlineStr">
+        <is>
+          <t>4331</t>
+        </is>
+      </c>
+      <c r="F42" s="12" t="inlineStr">
+        <is>
+          <t>6-5-0=1 0 6-3-0=3 0 8-5-0=3 0 9-5-0=4 0 4331</t>
+        </is>
+      </c>
+      <c r="G42" s="14" t="inlineStr">
+        <is>
+          <t>1分</t>
+        </is>
+      </c>
+      <c r="H42" s="10" t="inlineStr">
+        <is>
+          <t>基础4位完全正确</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="22" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B43" s="24" t="inlineStr">
+        <is>
+          <t>Sub4 (4位减法)</t>
+        </is>
+      </c>
+      <c r="C43" s="23" t="inlineStr">
+        <is>
+          <t>8845 - 7846 =</t>
+        </is>
+      </c>
+      <c r="D43" s="23" t="inlineStr">
+        <is>
+          <t>5-6-0=9 1 4-4-1=9 1 8-8-1=9 1 8-7-1=0 0</t>
+        </is>
+      </c>
+      <c r="E43" s="22" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="F43" s="23" t="inlineStr">
+        <is>
+          <t>5-6-0=9 1 4-4-1=9 1 8-8-1=9 1 8-7-1=0 0 999</t>
+        </is>
+      </c>
+      <c r="G43" s="14" t="inlineStr">
+        <is>
+          <t>1分</t>
+        </is>
+      </c>
+      <c r="H43" s="21" t="inlineStr">
+        <is>
+          <t>3级连续借位退位完全正确</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>